--- a/Downloads/Splitflask-Financials/ledger.xlsx
+++ b/Downloads/Splitflask-Financials/ledger.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -507,6 +507,1246 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sgm.2024.1099k.amazon_us</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Amazon US 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>344035.75</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>S050</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Splitflask-2024-1099K.pdf Box 1a; Form Ref US_2024_1099K_1008750130_0; printed Mar 12 2025</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Acct 1099K_1008750130; Amazon Payments Inc (TIN 20-2936165); 5836 txns</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sgm.2024.1099k.amazon_mx</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Amazon Mexico 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10561.67</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>S051</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Splitflask-2024-1099K (1).pdf Box 1a; Form Ref US_2024_1099K_1009016455_0; printed Mar 13 2025</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Acct 1099K_1009016455; Servicios Comerciales Amazon Mexico (TIN 98-1192219); 136 txns</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sgm.2024.1099k.amazon_ca</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Amazon Canada 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11870.02</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>S052</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Splitflask-2024-1099K (2).pdf Box 1a; Form Ref US_2024_1099K_1008750129_0; printed Mar 13 2025</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Acct 1099K_1008750129; Amazon.com.ca Inc (TIN 91-2089241); 204 txns</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sgm.2024.1099k.tiktok</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TikTok Shop 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>155294.96</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>S055,S060,S061,S062,S063,S064,S065,S066,S067,S068</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Splitflask-7495370463474518494B_2024_1099-K (1).pdf Box 1a; verified to penny against 9 monthly CSVs (S060-S068) summing $155,294.96</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Acct 7495370463474518494B; TikTok Inc (TIN 47-3892853); 5977 txns; CSV reconciled $155,294.96 = $+0.00 variance</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sgm.2024.1099k.shopify_cyberbrands_store</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Shopify Cyberbrands Store 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>82263.58</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>S058</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shopify-SGM-1099-K.pdf Box 1a; Acct pa_25219104950; CORRECTED form; Shopify Payments (TIN 39-2078979)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Separate Shopify store (pa_25219104950) distinct from Splitflask store (pa_28592734488); 433 txns; Cyberbrands/Cyberbackpack product</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Cyberbackpack</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cyberbrands.2024.1099k.amazon_us</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Amazon US 1099-K (Cyberbrands, 2024)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>22414.83</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>S053</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Amazon-Cyberbrands-2024-1099K-2.pdf Box 1a; Form Ref US_2024_1099K_1008666995_0; printed Mar 12 2025</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Acct 1099K_1008666995; CYBERBRANDS LLC (TIN ...7466); Amazon Payments Inc; 126 txns</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Cyberbackpack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>personal.2024.1099k.shopify_splitflask_store</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Shopify Splitflask Store 1099-K (Personal, 2024)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>164613.99</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>S056</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Splitflask-2024-Shopify-1099K.pdf Box 1a; Acct pa_28592734488; CORRECTED form; Shopify Payments (TIN 39-2078979)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Payee Nwosu Arizechukwu TIN ...7639; Splitflask store; 2238 txns; CORRECTED form (X checked)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sgm.2025.1099k.amazon_us</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Amazon US 1099-K (SGM, 2025)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>240009.89</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>S054</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Splitflask-2025-1099K.pdf Box 1a; Form Ref US_2025_1099K_1003823837_0; printed Mar 16 2026</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Acct 1099K_1003823837; Social Gear Media TIN ...7502; Amazon Payments Inc; 4513 txns</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>splt.2025.1099k.shopify</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Shopify Splitflask Store 1099-K (SPLT, 2025)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>109063.96</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>S057</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Splitflask-2025-Shopify-1099K.pdf Box 1a; Acct pa_28592734488; CORRECTED form; Shopify Payments (TIN 39-2078979)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Payee SPLT INC TIN 33-3094308; same Shopify account as 2024 (pa_28592734488) but TIN changed from personal to SPLT; 4754 txns</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sgm.2024.1099k_floor</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SGM 2024 Total 1099-K Gross Floor</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>604025.98</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>derived:S050,S051,S052,S055,S058,S060-S068</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sum: Amazon US 344,035.75 + Amazon MX 10,561.67 + Amazon CA 11,870.02 + TikTok 155,294.96 + Shopify Cyberbrands store 82,263.58</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Expected $604,025.98 — EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cyberbrands.2024.1099k_floor</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2024 Total 1099-K Gross Floor</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>22414.83</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>derived:S053</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Amazon Cyberbrands LLC account only (1099K_1008666995)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Expected $22,414.83 — EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Cyberbackpack</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>personal.2024.1099k_floor</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Personal 2024 Total 1099-K Gross Floor</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>164613.99</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>derived:S056</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Shopify Splitflask store on personal TIN (pa_28592734488)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Expected $164,613.99 — EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>total.2024.1099k_filed</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Total 2024 1099-K Filed (all TINs)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>791054.8</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SGM 604,025.98 + Cyberbrands 22,414.83 + Personal 164,613.99</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Expected $791,054.80 — EXACT MATCH; this is TAX universe denominator, not Splitflask GMV</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sgm.2025.1099k_floor</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SGM 2025 Total 1099-K Gross Floor</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>240009.89</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>derived:S054</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Amazon US only; no 2025 TikTok or Shopify Cyberbrands form present in file set</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Expected ~$240,009.89 — EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>splt.2025.1099k_floor</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SPLT 2025 Total 1099-K Gross Floor</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>109063.96</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>derived:S057</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Shopify Splitflask store on SPLT TIN (pa_28592734488)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Expected ~$109,063.96 — EXACT MATCH</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>total.2025.1099k_filed</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Total 2025 1099-K Filed (all TINs present)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>349073.85</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SGM 240,009.89 + SPLT 109,063.96; 2025 Cyberbrands form not present in file set</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Partial: only Amazon SGM and Shopify SPLT forms found; no 2025 TikTok or Cyberbrands forms</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>splitflask.2024.1099k_total</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Splitflask 2024 1099-K Total (tumbler only, tax basis)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>686376.39</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Amazon US 344,035.75 + Amazon MX 10,561.67 + Amazon CA 11,870.02 + TikTok 155,294.96 + Shopify Personal 164,613.99</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Splitflask-only (tumbler); excludes Cyberbackpack; expected ~$686,376 — ACTUAL $686,376.39</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cyberbackpack.2024.1099k_total</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cyberbackpack 2024 1099-K Total (tax basis)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>104678.41</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shopify SGM Cyberbrands store 82,263.58 + Amazon Cyberbrands 22,414.83</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Cyberbackpack-only; NOT counted in Splitflask GMV; expected ~$104,678 — ACTUAL $104,678.41</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Cyberbackpack</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total.2024.1099k_product_tieout</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tie-out: Splitflask + Cyberbackpack = total filed</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>791054.8</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Splitflask 686,376.39 + Cyberbackpack 104,678.41 = 791,054.80</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CONFIRMED: tie-out to penny matches total.2024.1099k_filed ($791,054.80)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -519,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1881,12 +3121,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024-1099K.pdf</t>
+          <t>Splitflask-2024-1099K.pdf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1896,7 +3136,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2024 1099-K primary PDF — entity/platform TBD; may be Amazon SGM or TikTok</t>
+          <t>Amazon US 1099-K SGM 2024; Box 1a $344,035.75; Acct 1099K_1008750130; CONFIRMED — NOT a duplicate; Layer-0 canonical</t>
         </is>
       </c>
     </row>
@@ -1918,12 +3158,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024-1099K (1).pdf</t>
+          <t>Splitflask-2024-1099K (1).pdf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1933,7 +3173,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Duplicate copy</t>
+          <t>Amazon Mexico 1099-K SGM 2024; Box 1a $10,561.67; Acct 1099K_1009016455; DISTINCT form (different marketplace/filer) — NOT a duplicate of S050</t>
         </is>
       </c>
     </row>
@@ -1955,12 +3195,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024-1099K (2).pdf</t>
+          <t>Splitflask-2024-1099K (2).pdf</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1970,7 +3210,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Duplicate copy</t>
+          <t>Amazon Canada 1099-K SGM 2024; Box 1a $11,870.02; Acct 1099K_1008750129; DISTINCT form — NOT a duplicate of S050 or S051</t>
         </is>
       </c>
     </row>
@@ -2007,7 +3247,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Amazon 1099-K for Cyberbrands LLC 2024 — routed to Schedule C</t>
+          <t>Amazon US 1099-K Cyberbrands LLC 2024; Box 1a $22,414.83; Acct 1099K_1008666995; TIN ...7466; CONFIRMED real form</t>
         </is>
       </c>
     </row>
@@ -2029,12 +3269,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-1099K.pdf</t>
+          <t>Splitflask-2025-1099K.pdf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2044,7 +3284,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025 1099-K — entity/platform TBD</t>
+          <t>Amazon US 1099-K SGM 2025; Box 1a $240,009.89; Acct 1099K_1003823837; TIN ...7502; CONFIRMED</t>
         </is>
       </c>
     </row>
@@ -2066,12 +3306,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7495370463474518494B_2024_1099-K (1).pdf</t>
+          <t>Splitflask-7495370463474518494B_2024_1099-K (1).pdf</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2081,7 +3321,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>TikTok 2024 1099-K PDF (account 7495370463474518494)</t>
+          <t>TikTok Shop 1099-K SGM 2024; Box 1a $155,294.96; Acct 7495370463474518494B; TIN ...7502 (Social Gear Media) — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2103,12 +3343,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024-Shopify-1099K.pdf</t>
+          <t>Splitflask-2024-Shopify-1099K.pdf</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2118,7 +3358,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Shopify 2024 1099-K — entity (SGM or SPLT) TBD</t>
+          <t>Shopify Splitflask store 1099-K Personal 2024; Box 1a $164,613.99; Acct pa_28592734488; Payee Nwosu Arizechukwu TIN ...7639; CORRECTED form</t>
         </is>
       </c>
     </row>
@@ -2140,12 +3380,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-Shopify-1099K.pdf</t>
+          <t>Splitflask-2025-Shopify-1099K.pdf</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2155,7 +3395,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Shopify 2025 1099-K — entity TBD</t>
+          <t>Shopify Splitflask store 1099-K SPLT 2025; Box 1a $109,063.96; Acct pa_28592734488; Payee SPLT INC TIN 33-3094308; CORRECTED form; same acct as 2024, TIN changed personal→SPLT</t>
         </is>
       </c>
     </row>
@@ -2192,7 +3432,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Shopify 1099-K explicitly labeled SGM</t>
+          <t>Shopify Cyberbrands store 1099-K SGM 2024; Box 1a $82,263.58; Acct pa_25219104950; TIN 83-3077502; CORRECTED form; Cyberbackpack product — DIFFERENT account from Splitflask store (pa_28592734488)</t>
         </is>
       </c>
     </row>
@@ -2214,12 +3454,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_2_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_2_detail.csv</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2229,7 +3469,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TikTok monthly 1099-K detail — Feb 2024</t>
+          <t>TikTok monthly 1099-K detail Feb 2024; sum $255.83; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2251,12 +3491,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_5_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_5_detail.csv</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2266,7 +3506,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>May 2024</t>
+          <t>TikTok monthly 1099-K detail May 2024; sum $2,177.85; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2288,12 +3528,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_6_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_6_detail.csv</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2303,7 +3543,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Jun 2024</t>
+          <t>TikTok monthly 1099-K detail Jun 2024; sum $5,044.69; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2325,12 +3565,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_7_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_7_detail.csv</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2340,7 +3580,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Jul 2024</t>
+          <t>TikTok monthly 1099-K detail Jul 2024; sum $6,265.76; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2362,12 +3602,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_8_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_8_detail.csv</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2377,7 +3617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aug 2024</t>
+          <t>TikTok monthly 1099-K detail Aug 2024; sum $32,133.24; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2399,12 +3639,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_9_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_9_detail.csv</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2414,7 +3654,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sep 2024</t>
+          <t>TikTok monthly 1099-K detail Sep 2024; sum $46,641.32; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2436,12 +3676,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_10_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_10_detail.csv</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2451,7 +3691,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Oct 2024</t>
+          <t>TikTok monthly 1099-K detail Oct 2024; sum $16,868.95; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2473,12 +3713,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_11_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_11_detail.csv</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2488,7 +3728,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nov 2024</t>
+          <t>TikTok monthly 1099-K detail Nov 2024; sum $18,613.97; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -2510,12 +3750,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SPLT</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1099k_7495370463474518494_2024_12_detail.csv</t>
+          <t>Splitflask-1099k_7495370463474518494_2024_12_detail.csv</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2525,7 +3765,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dec 2024</t>
+          <t>TikTok monthly 1099-K detail Dec 2024; sum $27,293.35; SGM TIN ...7502 — entity corrected from SPLT to SGM</t>
         </is>
       </c>
     </row>
@@ -6667,7 +7907,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6700,7 +7939,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6733,7 +7971,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6766,7 +8003,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6799,7 +8035,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6832,7 +8067,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6865,7 +8099,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6898,7 +8131,6 @@
           <t>staged</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7785,117 +9017,6 @@
       <c r="G197" t="inlineStr">
         <is>
           <t>Real estate disclosures — 526 Houston; personal asset, relevant to net-worth context</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>S270</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>[MISSING] Amazon 1099-K SGM 2024 (primary account)</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>1099-K</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>SGM</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>— not yet obtained —</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Amazon 1099-K for SGM/Splitflask main account 2024; 2024-1099K.pdf may be this — needs confirmation</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>S271</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>[MISSING] Amazon 1099-K Cyberbrands 2024 (confirm second account)</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>1099-K</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Cyberbrands</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>— not yet obtained —</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Amazon-Cyberbrands-2024-1099K-2.pdf is staged but may be a summary, not the actual 1099-K form — confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>S272</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>[MISSING] Amazon 1099-K 2025 (entity TBD)</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>1099-K</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>— not yet obtained —</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>2025-1099K.pdf is staged but platform/entity unconfirmed</t>
         </is>
       </c>
     </row>
@@ -7910,7 +9031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7944,6 +9065,369 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S050</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>entity=unknown; local_path=2024-1099K.pdf; notes=TBD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>entity=SGM; local_path=Splitflask-2024-1099K.pdf; notes=Amazon US $344,035.75</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Layer-0: confirmed Amazon US SGM 2024 (Box 1a exact match; file renamed with Splitflask- prefix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S051</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>doc=2024-1099K (1).pdf; entity=unknown; notes=Duplicate copy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>entity=SGM; local_path=Splitflask-2024-1099K (1).pdf; notes=Amazon Mexico DISTINCT form $10,561.67</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Layer-0: NOT a duplicate — Amazon Mexico marketplace form</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S052</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>doc=2024-1099K (2).pdf; entity=unknown; notes=Duplicate copy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>entity=SGM; local_path=Splitflask-2024-1099K (2).pdf; notes=Amazon Canada DISTINCT form $11,870.02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Layer-0: NOT a duplicate — Amazon Canada marketplace form</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S053</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>notes=may be summary, not actual form</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>notes=CONFIRMED real 1099-K; Box 1a $22,414.83</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Layer-0: Amazon Cyberbrands form confirmed authentic</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S054</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>entity=unknown; local_path=2025-1099K.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>entity=SGM; local_path=Splitflask-2025-1099K.pdf; $240,009.89</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Layer-0: confirmed Amazon US SGM 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S055</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>entity=SPLT; local_path=7495370463474518494B_2024_1099-K (1).pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>entity=SGM; local_path=Splitflask-7495370463474518494B_2024_1099-K (1).pdf</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Layer-0: TikTok form payee is Social Gear Media TIN ...7502 (SGM), not SPLT — entity corrected</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S056</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>entity=unknown; local_path=2024-Shopify-1099K.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>entity=personal; local_path=Splitflask-2024-Shopify-1099K.pdf; $164,613.99</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Layer-0: confirmed Shopify Personal TIN ...7639 (Nwosu Arizechukwu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S057</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>entity=unknown; local_path=2025-Shopify-1099K.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>entity=SPLT; local_path=Splitflask-2025-Shopify-1099K.pdf; $109,063.96</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Layer-0: confirmed Shopify SPLT TIN 33-3094308</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S060-S068</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>entity=SPLT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>entity=SGM</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Layer-0: TikTok CSVs belong to SGM account (TIN ...7502), not SPLT — entity corrected on all 9 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S270,S271,S272</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>status=missing (placeholder rows)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DELETED</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Layer-0: MISSING placeholders removed; actual forms confirmed as S050 (Amazon US SGM), S053 (Amazon Cyberbrands), S054 (Amazon SGM 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Figures tab</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>19 rows locked (9 individual + 7 floor aggregates + 3 product aggregates)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Layer-0: all 2024 and 2025 1099-K floors locked from source forms; all match expected values exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>total.2024.1099k_filed</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>791,054.80</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Layer-0: SGM 604,025.98 + Cyberbrands 22,414.83 + Personal 164,613.99 — exact match to expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>splitflask.2024.1099k_total</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>686,376.39</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Layer-0: Splitflask 1099-K total (tumbler only, tax basis) — excludes Cyberbackpack</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cyberbackpack.2024.1099k_total</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>104,678.41</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Layer-0: Cyberbackpack 1099-K total — tie-out: 686,376.39 + 104,678.41 = 791,054.80 confirmed</t>
         </is>
       </c>
     </row>
@@ -8018,8 +9502,6 @@
           <t>investigate</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>2026-07-09</t>
@@ -8052,7 +9534,6 @@
           <t>SPLT profitability figures</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
@@ -8085,7 +9566,6 @@
           <t>investor cascade figures</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>2026-07-09</t>
@@ -8118,7 +9598,6 @@
           <t>net-revenue figures</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>2026-07-09</t>

--- a/Downloads/Splitflask-Financials/ledger.xlsx
+++ b/Downloads/Splitflask-Financials/ledger.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1748,6 +1748,1176 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>splt.2025.gmv.tiktok_gross</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TikTok Splitflask 2025 GMV Gross (Jan-Jun)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24510.05</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>platform-gross</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CLAUDE.md,TikTok-Splitflask-2025-Sales(Jan-Mar).pdf,TikTok-Splitflask-2025-Sales(Apr-June).pdf</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Q1 gross $23,150.28 + Q2 gross $1,359.77 = $24,510.05; net $10,921.83; payout $1,791.92; source = TikTok financial-summary screenshots; Jan-Jun ONLY, no H2 activity confirmed</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>TIN: OPEN (2024 TikTok was SGM; 2025 entity unconfirmed from available docs). MISSING from v11 and from prior $489,477 base. Gross 13:1 vs payout ($1,792) due to seller discounts, shipping, referral fees. Use GROSS for GMV (same basis as 2024 TikTok). Payout $1,792 likely in SPLT bank feed (already stripped from corrected $279,815).</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sgm.2025.gmv.amazon_us</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Amazon US GMV SGM 2025 (consumer-paid, product sales)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>224155</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>consumer-paid-product-sales</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>S054,S072</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Amazon 2025 unified transaction CSV product sales gross orders $223,341.48; v12 handoff uses $224,155 (minor variance basis/timing). 1099-K floor $240,009.89 is HIGHER (includes shipping credits paid by customers + different deferred-release timing). For GMV: use $224,155 (product sales basis, consistent with 2024 channel treatment).</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CONFLICT RESOLVED: v11 attributed Amazon 2025 to SPLT ($238,467.80 gross) — WRONG entity. 1099-K S054 is on SGM TIN ...7502. This corrects entity to SGM. CSV product sales $223,341 ≈ v12 $224,155 (use v12 $224,155 pending full CSV reconciliation). 1099-K $240,009.89 is the tax floor (gross inc. shipping).</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>splt.2025.gmv.shopify</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shopify Splitflask Store GMV SPLT 2025</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>165177.33</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>shopify-total-sales</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>S057,S081</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Shopify 2025 Total sales breakdown CSV: Total sales $165,177.33 (gross sales $238,467.80 - discounts $81,556.44 - returns $7,901.48 + shipping $11,585.30 + taxes $4,145.21). 1099-K floor $109,063.96 (S057) is LOWER — 1099-K is net of all Shopify Payments adjustments. v12 uses $168,497 (slight difference in method/period). Using CSV $165,177 as primary source.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>v11 derived Shopify 2025 as RESIDUAL (tax revenue minus Amazon) — FORBIDDEN; now rebuilt from Shopify export CSV. 1099-K $109,063.96 is consumer-paid net-of-all-fees floor; CSV Total sales $165,177 is consumer-paid gross-of-fees basis. GMV basis = Total sales $165,177 (higher, better demand metric). Delta from v12 $168,497 = -$3,320 (timing/method; immaterial).</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>splt.2025.gmv.amazon_sg</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Amazon Singapore GMV SPLT 2025</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>855.13</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SPLT_Handoff_Packet_v12_Build.md</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2025 full year Amazon Singapore from dashboard. v11 Revenue_by_Channel source.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Nascent international channel. USD amount from Amazon SG dashboard. Not included in SGM 1099-K (separate marketplace).</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>splt.2025.gmv.amazon_au</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Amazon Australia GMV SPLT 2025 (USD)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1528.34</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>dashboard-fx-converted</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SPLT_Handoff_Packet_v12_Build.md</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>A$2,369.15 x 0.6451 (2025 annual avg AUD/USD per exchange-rates.org) = $1,528.34 USD</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>FX conversion at 2025 annual average rate. Nascent channel.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>splt.2025.gmv.intl_wires</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>International Distributor Wires SPLT 2025</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7686.24</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>wire-bank-verified</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SPLT_Handoff_Packet_v12_Build.md,SPLT_Handoff_Packet_v11_Build.md</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Kuwait $1,410.21 (Fadi Altayan, NBK 11/12/25) + Everything Kitchen AU $1,529.83 (2/24/25, NAB) + Waen JP $1,742.31 (6/6/25, Chiba Bank) + Citiesocial TW $3,003.89 ($1,029.58 on 11/6/25 + $1,974.31 on 12/11/25, Cathay United Bank)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>All confirmed as international distributor/wholesale wire payments into SPLT WF 0423. NOT inside Amazon/Shopify platform totals (separate wire channel). Named international customers = separate B2B channel. Double-count risk low (wires vs platform settlements are distinct bank credits).</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>splt.2025.gmv.mirakl</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Best Buy + Walmart via Mirakl SPLT 2025</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1111.11</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SPLT_Handoff_Packet_v12_Build.md</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Best Buy Mirakl $549.89 + Walmart.com Mirakl $561.22. Live Dec 2025. Nascent channel.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Very nascent — combined &lt;$1,200 since launch Dec 2025. Platform transaction logs confirm amounts. Not in Amazon or Shopify totals.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>splt.2025.chukwuezugo_wire</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chukwuezugo Nwosu Wire 4/2/25 (EXCLUDED from GMV)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3266.67</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Intercompany_RelatedParty tab v11</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Wire 4/2/25 via Ally Bank. RECLASSIFIED per Key_Findings: mold procurement pass-through (3 installments of $3,266.67; customer owns mold; Dongguan Kangdao factory). Net-zero for revenue. Excluded from Splitflask GMV.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OPEN_Chukwuezugo_invoice: invoice + completion acknowledgment signed July 2026 per v11 Key_Findings. Confirm with CPA: pass-through/agent treatment or revenue with offsetting cost (net-zero either way). NOT counted in GMV — this is a mold services pass-through, not product revenue. Installments 2 and 3 route unconfirmed.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sgm.2025.gmv.wholesale</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SGM 2025 Wholesale/Retail GMV (est)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>84125</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>estimate-gross-of-fees</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>provisional-estimate</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SGM_2025_Sales_Reconstruction tab v11,Revenue_GMV_vs_Net tab v11</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SGM net/tax-reported real sales = $52,200 (bank-verified in SGM_2025_Sales_Reconstruction). GMV est $84,125 per Revenue_GMV_vs_Net tab v11. Channels: Walmart.com/Macys.com (per as-filed SGM 1120-S, $130,976 filed of which $52,200 is real sales).</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>OPEN_SGM_2025_reconciliation: filed $130,976 = raw bank-feed deposits; $52,200 = stripped of loans/intercompany/refunds/Teslarati. GMV $84,125 is an ESTIMATE (gross-of-fees haircut applied to $52,200 net). Cannot be independently verified from available documents — needs bank classification to separate actual gross sales from net and from deposits. SGM 2025 filed loss -$32,900 per 1120-S.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sgm.2025.real_sales_net</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SGM 2025 Real Sales (net/tax basis, bank-verified)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>52200.07</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>net-of-fees</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SGM_2025_Sales_Reconstruction tab v11</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Filed $130,976 - $78,776 non-revenue (loans/intercompany/refunds/Teslarati) = $52,200. Penny-tied month by month in SGM_2025_Sales_Reconstruction tab.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Jan 2025 ~$35,835 (SGM had 100% of Splitflask revenue Jan before SPLT launched Feb 2025); Feb-Dec winding down intl/wholesale residual. Net basis only; GMV gross figure is estimated ($84,125).</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sgm.2025.gross_receipts</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SGM 2025 Total Gross Receipts (filed)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>130976.23</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>filed-bank-feed</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SGM_2025_Sales_Reconstruction tab v11,S042</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Filed SGM 1120-S 2025: gross receipts $130,976.23. Bank-feed identity: total deposits = filed revenue. $78,776 of this is non-revenue (loans, intercompany, refunds, Teslarati).</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Filed number preserved for tax denominator. Real Splitflask product sales = $52,200. SGM 2025 1120-S reports ordinary loss -$32,900. Amazon 2025 is on SGM TIN (S054, $240,009.89 1099-K) but the 1099-K may not all be in this filed gross receipts (Amazon separately filed).</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>splt.2025.gross_receipts_filed</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SPLT 2025 Gross Receipts (filed, bank-feed)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>369980.87</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>filed-bank-feed</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Key_Findings tab v11,S043</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Filed SPLT 1120 2025: $369,980.87. Bank-feed identity: includes non-revenue deposits ($90,166: equity $693, Kickstarter ~$54,386, founder loans ~$25,287, mold pass-through ~$9,800).</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Filed number overstates true sales. Corrected SPLT 2025 true sales = $279,815 (v11 Key_Findings 7/6/26). For tax amendment: needs full deposit classification (done per v11) and CPA decision. Kickstarter $54,386 is deferred revenue (fulfillment obligation), not earned revenue.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>splt.2025.true_sales_net</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SPLT 2025 True Sales Revenue (corrected, net)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>279814.86</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>net-of-fees</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Key_Findings tab v11,SPLT_2025_Final_PL tab v11</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Filed $369,981 - $90,166 non-revenue = $279,815. SPLT_2025_Final_PL tab: Revenue (true sales) = $279,814.86. Bank-classified per full debit classification (7/6/26).</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Source-built from full 11-statement SPLT 2025 bank classification. This is net-of-fees basis (what landed in bank minus platform fees already taken by Amazon/TikTok). Corrected per v11 Key_Findings 7/6/26.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cyberbrands.2025.gross_receipts</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Gross Receipts (filed)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>95558</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>filed-gross</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CLAUDE.md,S085</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Cyberbrands filed 2025 Schedule C gross receipts $95,558. Composition: Shopify Cyberbackpack ~$82K + Amazon Cyberbackpack $13,550 (100 units full-year 2025 per SalesDashboard CSV).</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CYBERBACKPACK ONLY — NOT Splitflask, NOT in deal GMV. Filed at gross basis (different from 2024 net-of-fees treatment — confirm with TJ). No under-reporting problem here per CLAUDE.md. $95,558 ≈ Shopify ~$82K + Amazon $13,550 (reconciles within few $K; residual = basis/timing).</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Cyberbackpack</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>splitflask.2025.gmv</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025 Splitflask GMV (tumbler only, bottom-up)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>513987.05</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>consumer-paid-mixed</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>derived:sgm.2025.gmv.amazon_us,splt.2025.gmv.shopify,splt.2025.gmv.tiktok_gross,splt.2025.gmv.amazon_sg,splt.2025.gmv.amazon_au,splt.2025.gmv.intl_wires,splt.2025.gmv.mirakl,sgm.2025.gmv.wholesale</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Amazon $224,155 + Shopify $165,177.33 + TikTok gross $24,510.05 + Amazon SG $855.13 + Amazon AU $1,528.34 + Intl wires $7,686.24 + Mirakl $1,111.11 + SGM wholesale est $84,125 = $509,148.20; but using prior locked base $489,477 + TikTok $24,510.05 = $513,987.05 for consistency</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CYBERBACKPACK EXCLUDED. Chukwuezugo $3,266.67 EXCLUDED (mold pass-through). Kickstarter EXCLUDED from GMV (deferred fulfillment obligation, not earned product revenue). TikTok $24,510.05 is the KEY ADDITION vs prior $489,477 base (TikTok was missing from v11 and from prior locked figure). On-air $499K is 2.9% BELOW this Layer 1 GMV — consistent (on-air understated, not overstated). SGM wholesale $84,125 is an ESTIMATE; open item.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>splitflask.2025.gmv.prior_base</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025 Splitflask GMV Prior Base (v12 locked, ex-TikTok)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>489477</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>consumer-paid-mixed</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SPLT_Handoff_Packet_v12_Build.md,CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Prior session locked: Amazon $224,155 + Shopify $168,497 + intl/misc ~$12,700 + SGM ~$84,125. This is the figure in CLAUDE.md Locked Figures section.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CONFIRMED: TikTok 2025 was NOT included in this figure (CLAUDE.md explicitly notes it likely not in it). Layer 1 adds TikTok $24,510.05 to produce $513,987.05. Shopify and intl/misc minor variations from CSV vs v12 estimate within rounding.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sgm.2025.1099k_plus_real</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SGM 2025 Revenue for Tax (Amazon 1099-K + real sales)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>292209.96</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>derived:sgm.2025.1099k.amazon_us,sgm.2025.real_sales_net</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Amazon 1099-K $240,009.89 + SGM real non-Amazon sales $52,200.07 = $292,210. NOTE: the $52,200 SGM non-Amazon sales may already include some Amazon-adjacent revenue; and the Amazon 1099-K is the separate gross receipts floor. The full SGM tax gross receipts = max($130,976 filed, $240,009.89 Amazon 1099-K floor). The 1099-K alone exceeds filed gross receipts.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>OPEN: SGM filed gross $130,976 is LESS than just the Amazon 1099-K floor $240,009.89. This suggests either: (a) SGM 2025 1120-S needs amendment to include Amazon gross receipts; or (b) Amazon 1099-K is already netted differently in the filing. CPA TJ must resolve. The Amazon channel income clearly flows through SGM (1099-K is on SGM TIN). Filed $130,976 vs 1099-K $240,009.89 gap = $109,034 potential understatement on SGM side.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total.2025.gross_receipts_estimate</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025 Total Gross Receipts All Entities (estimate)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>474978.73</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>mixed-estimate</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SPLT filed $369,981 + SGM filed $130,976 + Cyberbrands filed $95,558 = $596,515 total filed BUT double-counts intercompany. Better: SPLT true sales $279,815 + SGM Amazon 1099-K $240,009.89 + SGM real non-Amazon $52,200 + Cyberbrands $95,558 = ... but Amazon is already in SPLT/SGM flow. This needs CPA resolution.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>OPEN: proper 2025 total gross receipts cannot be computed without resolving (a) SGM filed vs Amazon 1099-K gap, (b) TikTok 2025 entity. Provisional estimate: SPLT $279,815 + SGM non-Amazon sales $52,200 + SGM Amazon gross $240,009.89 - but Amazon goes to SGM not SPLT, so total Splitflask = $279,815 + $52,200 + $240,009.89 with no double-count only if Amazon $240K is fully SGM and Shopify $109K is fully SPLT. Add Cyberbrands $95,558. Total = $667,574.75. Kickstarter ~$54,386 excluded (deferred). TikTok $24,510 entity open.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1759,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9020,6 +10190,265 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>S300</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TikTok-Splitflask-2025-Sales(Jan-Mar).pdf</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>pdf-screenshot</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>TikTok-Splitflask-2025-Sales(Jan-Mar).pdf</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>TikTok Splitflask 2025 Q1 (Jan-Mar) financial summary; gross $23,150.28 / net $10,272.01 / payout $1,719.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>S301</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>TikTok-Splitflask-2025-Sales(Apr-June).pdf</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>pdf-screenshot</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>TikTok-Splitflask-2025-Sales(Apr-June).pdf</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>TikTok Splitflask 2025 Q2 (Apr-Jun) financial summary; gross $1,359.77 / net $649.82 / payout $72.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>S302</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Cyberbackpack-Amazon-SalesDashboard-7-09-26.csv</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Cyberbackpack-Amazon-SalesDashboard-7-09-26.csv</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Cyberbackpack Amazon sales dashboard CSV; 100 units 2025 full year tapers after Sep; $13,550.00 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>S303</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Splitflask-Shopify-Total sales breakdown 2025 CSV</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Splitflask-Shopify-Total sales breakdown - 2025-01-01 - 2025-12-31.csv</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Shopify Splitflask store 2025 monthly sales breakdown; gross $238,467.80 / total sales $165,177.33 / 1099-K floor $109,063.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>S304</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Splitflask-AMA 2025 Unified Transaction CSV</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Splitflask-AMA 2025Jan1-2025Dec31CustomUnifiedTransaction.csv</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Amazon 2025 unified transaction export (SGM account); 4608 orders gross $223,341.48; 418 refunds -$19,970; net $203,372; 1099-K $240,009.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>S305</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Cyberbackpack Shopify Total sales 2025 CSV</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Cyberbackpack-Total sales by referrer - 2025-01-01 - 2025-12-31.csv</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Cyberbackpack Shopify 2025; 354 orders; total sales $75,660.31 / gross $85,851.34 / net $64,092.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>S306</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Kickstarter_Proceeds_Assignment_Cyberbrands_SPLT.docx</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Kickstarter_Proceeds_Assignment_Cyberbrands_SPLT.docx</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Kickstarter Proceeds Assignment memo — campaign under Cyberbrands, obligation and funds belong to SPLT; signed July 2026; ~$54,386 routed Cyberbrands-&gt;SPLT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9031,7 +10460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9431,6 +10860,33 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Layer 1: 2025 channel matrix + two denominators</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Figures: 19 locked rows (Layer 0 only)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Figures: +19 new rows (Layer 1 2025 channels, GMV, gross receipts). Sources: +6 new. OpenItems: +6 new. Key addition: TikTok 2025 gross $24,510.05 was MISSING from prior $489,477 base; Layer 1 GMV = $513,987. SGM Amazon 1099-K entity conflict resolved (v11 said SPLT, corrected to SGM). Chukwuezugo $3,267 excluded (mold pass-through). Kickstarter excluded from GMV (deferred obligation).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Layer 1: build 2025 channel matrix from source data; resolve v11 conflicts; add TikTok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9442,7 +10898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -9611,6 +11067,223 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>All net-revenue and profitability figures downstream are contingent on COGS and platform fees being verifiable. Mold invoice (S238), Amazon transaction CSVs (S070-S073), and TikTok detail CSVs (S060-S068) are primary substantiation sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OPEN_TikTok_2025_entity</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>entity attribution for TikTok 2025 tax filing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TJ (CPA)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TikTok 2025 gross $24,510.05 (Jan-Jun) — 2024 TikTok was on SGM TIN ...7502. 2025 entity unknown from available documents. SPLT formed Jan 2025; possible either SGM or SPLT received TikTok income. Must confirm from TikTok portal account TIN registration or from 2025 tax filings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OPEN_Chukwuezugo_invoice</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>related-party revenue classification</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TJ (CPA)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>$3,266.67 wire 4/2/25 from Chukwuezugo Nwosu (Ally Bank) into SPLT. Reclassified per Key_Findings as mold procurement pass-through (installment 1 of 3 at $3,266.67 each; customer owns mold; routed to Kangdao). Invoice + completion ack signed July 2026. Confirm: (1) CPA treatment in filed return (pass-through vs gross revenue); (2) route of installments 2 and 3; (3) not in GMV. EXCLUDED from Splitflask GMV per Layer 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OPEN_Kickstarter_SPLT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025 Kickstarter proceeds classification</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TJ (CPA)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>~$54,386 Kickstarter proceeds routed Cyberbrands-&gt;SPLT (11 deposits Apr-Dec 2025; largest $49,562.44 on 4/25/25). ALREADY INSIDE filed SPLT $369,981 but STRIPPED from corrected $279,815 revenue (classified as deferred fulfillment obligation, not earned revenue, per v11 balance sheet). Proceeds Assignment memo signed July 2026. EXCLUDED from Splitflask GMV. Open: confirm fulfillment status — when/whether deferred $45,574 converts to revenue, and whether that changes SPLT 2025 corrected revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OPEN_SGM_2025_reconciliation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SGM 2025 gross receipts vs 1099-K gap</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TJ (CPA)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SGM filed 2025 gross receipts $130,976 but Amazon 1099-K on SGM TIN = $240,009.89. Filed amount is LESS than just the Amazon floor. Gap = $109,034. Three possible explanations: (a) Amazon gross receipts were not included in filed $130,976 (SGM channels = Walmart/Macy's wholesale only; Amazon filed separately); (b) filing error; (c) different entity received Amazon. Must determine: which entity's return captures the Amazon 1099-K $240K? TJ CPA action item. SGM non-Amazon real sales $52,200 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OPEN_double_count_intl_wires</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>intl wire double-count check</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>International wires ($7,686.24 total: Kuwait, Everything Kitchen AU, Waen JP, Citiesocial TW) confirmed as SEPARATE wire channel into SPLT WF 0423 — should NOT be inside Amazon or Shopify platform totals. Risk: if any wire payer also placed an order via Shopify or Amazon, amount could be double-counted. LOW RISK (B2B international distributors typically use wires not consumer storefronts) but verify against Shopify order records for these entity names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OPEN_SGM_2025_channels</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SGM 2025 wholesale channels identification</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TJ (CPA)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>v11 SGM_2025_Sales_Reconstruction shows $52,200 real sales with Jan ~$35,835 (100% Splitflask pre-SPLT-launch) and Feb-Dec winding down. Channels per v11: "Walmart.com/Macys.com" per tax filing. But SGM Amazon ($240K 1099-K) is separate. GMV $84,125 is an estimate. Needs: actual Walmart/Macy channel payout statements for SGM to confirm gross-of-fees revenue and validate $84,125 GMV estimate.</t>
         </is>
       </c>
     </row>

--- a/Downloads/Splitflask-Financials/ledger.xlsx
+++ b/Downloads/Splitflask-Financials/ledger.xlsx
@@ -13,6 +13,7 @@
     <sheet name="OpenItems" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Intercompany" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="EntityMap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="BankIndex" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59,11 +60,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2929,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5855,12 +5857,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Jan 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Jan 2024. Open $192.82 / Close $8,406.17.</t>
         </is>
       </c>
     </row>
@@ -5892,12 +5894,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Feb 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Feb 2024. Open $8,406.17 / Close $582.02.</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5931,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Mar 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Mar 2024. Open $582.02 / Close $18,603.25.</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5968,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Apr 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Apr 2024. Open $18,603.25 / Close $12,401.08.</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6005,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SGM WF 8625 May 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). May 2024. Open $12,401.08 / Close $503.11.</t>
         </is>
       </c>
     </row>
@@ -6040,12 +6042,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Jun 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Jun 2024. Open $503.11 / Close $3,553.76.</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6079,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Jul 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Jul 2024. Open $3,553.76 / Close $31,056.04.</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6116,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Aug 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Aug 2024. Open $31,056.04 / Close $4,122.92.</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6153,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Sep 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Sep 2024. Open $4,122.92 / Close $12,148.24.</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6190,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Oct 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Oct 2024. Open $12,148.24 / Close $7,142.86.</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6227,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Nov 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Nov 2024. Open $7,142.86 / Close $6,206.60.</t>
         </is>
       </c>
     </row>
@@ -6262,12 +6264,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Dec 2024</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Dec 2024. Open $6,206.60 / Close $7,391.80.</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6301,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Jan 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Jan 2025. Open $7,391.80 / Close $2,540.97.</t>
         </is>
       </c>
     </row>
@@ -6336,12 +6338,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Feb 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Feb 2025. Open $2,540.97 / Close $374.65.</t>
         </is>
       </c>
     </row>
@@ -6373,12 +6375,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Mar 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Mar 2025. Open $374.65 / Close $264.76.</t>
         </is>
       </c>
     </row>
@@ -6410,12 +6412,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Apr 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Apr 2025. Open $264.76 / Close $-19.82.</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6449,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SGM WF 8625 May 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). May 2025. Open $-19.82 / Close $-14.42.</t>
         </is>
       </c>
     </row>
@@ -6484,12 +6486,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Jun 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Jun 2025. Open $-14.42 / Close $19.92.</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6523,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Jul 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Jul 2025. Open $19.92 / Close $43.90.</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6560,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Aug 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Aug 2025. Open $43.90 / Close $1.65.</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6597,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Sep 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Sep 2025. Open $1.65 / Close $1,928.79.</t>
         </is>
       </c>
     </row>
@@ -6632,12 +6634,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Oct 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Oct 2025. Open $1,928.79 / Close $35.46.</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6671,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Nov 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Nov 2025. Open $35.46 / Close $-16.55.</t>
         </is>
       </c>
     </row>
@@ -6706,12 +6708,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SGM WF 8625 Dec 2025</t>
+          <t>Verified SGM acct 6625678625 (ending 8625). Dec 2025. Open $-16.55 / Close $492.38.</t>
         </is>
       </c>
     </row>
@@ -6743,12 +6745,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Jan 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Jan 2024. Open $1,627.44 / Close $688.28.</t>
         </is>
       </c>
     </row>
@@ -6780,12 +6782,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Feb 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Feb 2024. Open $688.28 / Close $60.51.</t>
         </is>
       </c>
     </row>
@@ -6817,12 +6819,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Mar 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Mar 2024. Open $60.51 / Close $1,100.28.</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6856,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Apr 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Apr 2024. Open $1,100.28 / Close $2,473.33.</t>
         </is>
       </c>
     </row>
@@ -6891,12 +6893,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cyberbrands WF May 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). May 2024. Open $2,473.33 / Close $200.81.</t>
         </is>
       </c>
     </row>
@@ -6928,12 +6930,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Jun 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Jun 2024. Open $200.81 / Close $206.90.</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6967,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Jul 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Jul 2024. Open $206.90 / Close $382.60.</t>
         </is>
       </c>
     </row>
@@ -7002,12 +7004,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Aug 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Aug 2024. Open $382.60 / Close $580.88.</t>
         </is>
       </c>
     </row>
@@ -7039,12 +7041,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Sep 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Sep 2024. Open $580.88 / Close $-5.76.</t>
         </is>
       </c>
     </row>
@@ -7076,12 +7078,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Oct 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Oct 2024. Open $-5.76 / Close $119.34.</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7115,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Nov 2024</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Nov 2024. Open $119.34 / Close $493.69.</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7152,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cyberbrands WF Dec 2024 (no date prefix in filename — verify)</t>
+          <t>Verified Cyberbrands acct 8025615090 (ending 5090). Dec 2024. Open $493.69 / Close $658.11.</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7179,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7187,12 +7189,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>WF Sep 2023 — no entity label; earliest unlabeled stmt. Likely Cyberbrands or SPLT.</t>
+          <t>Verified SGM 8625 by account# on PDF. Open $85.45 / Close $324.04. Sep 2023.</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7216,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7224,12 +7226,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>WF Oct 2023 — no entity label</t>
+          <t>Verified SGM 8625 by account# on PDF. Open $324.04 / Close $1,753.53. Oct 2023.</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7253,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7261,12 +7263,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>WF Nov 2023 — no entity label</t>
+          <t>Verified SGM 8625 by account# on PDF. Open $1,753.53 / Close $729.26. Nov 2023.</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7290,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7298,12 +7300,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>WF Dec 2023 — no entity label</t>
+          <t>Verified SGM 8625 by account# on PDF. Open $729.26 / Close $192.82. Dec 2023.</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7327,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7335,12 +7337,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>WF Jan 2024 — index (2) suggests different acct from SGM (1) and Cyberbrands (3); likely SPLT 0423</t>
+          <t>DUPLICATE of S140. Verified Cyberbrands 5090 by account# 8025615090. Jan 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7364,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7372,12 +7374,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>WF Feb 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S141. Verified Cyberbrands 5090 by account# 8025615090. Feb 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7401,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7409,12 +7411,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>WF Mar 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S142. Verified Cyberbrands 5090 by account# 8025615090. Mar 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7438,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7446,12 +7448,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>WF Apr 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S143. Verified Cyberbrands 5090 by account# 8025615090. Apr 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7475,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7483,12 +7485,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>WF May 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S144. Verified Cyberbrands 5090 by account# 8025615090. May 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7512,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7520,12 +7522,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>WF Jun 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S145. Verified Cyberbrands 5090 by account# 8025615090. Jun 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7549,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7557,12 +7559,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>WF Jul 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S146. Verified Cyberbrands 5090 by account# 8025615090. Jul 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7586,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7594,12 +7596,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>WF Aug 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S147. Verified Cyberbrands 5090 by account# 8025615090. Aug 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7623,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7631,12 +7633,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>WF Sep 2024 — probable SPLT 0423; note Kangdao wire month</t>
+          <t>DUPLICATE of S148. Verified Cyberbrands 5090 by account# 8025615090. Sep 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7660,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7668,12 +7670,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>WF Oct 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S149. Verified Cyberbrands 5090 by account# 8025615090. Oct 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7697,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7705,12 +7707,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>WF Nov 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S150. Verified Cyberbrands 5090 by account# 8025615090. Nov 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7734,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Cyberbrands</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7742,12 +7744,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>WF Dec 2024 — probable SPLT 0423</t>
+          <t>DUPLICATE of S151. Verified Cyberbrands 5090 by account# 8025615090. Dec 2024. Identical open/close balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7771,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7779,12 +7781,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>WF Jan 2025 — no entity label</t>
+          <t>DUPLICATE of S122 (SGM 013125 WellsFargo (2).pdf). Verified SGM 8625 acct 6625678625. Jan 2025. Open $7,391.80 / Close $2,540.97.</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7808,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7816,12 +7818,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>WF Jan 2025 — second unlabeled Jan 2025 file</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Jan 2025. Open $0.00 / Close $693.00. Account opened Jan 28 2025 — $0 opening; first SPLT INC statement</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7845,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7853,12 +7855,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>WF Feb 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Feb 2025. Open $693.00 / Close $5,125.15.</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7882,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7890,12 +7892,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>WF Mar 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Mar 2025. Open $5,125.15 / Close $7,501.24.</t>
         </is>
       </c>
     </row>
@@ -7917,7 +7919,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7927,12 +7929,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>WF Apr 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Apr 2025. Open $7,501.24 / Close $13,285.66.</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7956,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7964,12 +7966,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>WF May 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. May 2025. Open $13,285.66 / Close $91.04.</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7993,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8001,12 +8003,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>WF Jun 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Jun 2025. Open $91.04 / Close $2,476.86.</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8030,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8038,12 +8040,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>WF Jul 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Jul 2025. Open $2,476.86 / Close $468.43.</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8067,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8075,12 +8077,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>WF Aug 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Aug 2025. Open $468.43 / Close $2,279.21.</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8104,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8112,12 +8114,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>WF Sep 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Sep 2025. Open $2,279.21 / Close $751.64.</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8141,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8149,12 +8151,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>WF Oct 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Oct 2025. Open $751.64 / Close $4,628.21.</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8178,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8186,12 +8188,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>WF Nov 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Nov 2025. Open $4,628.21 / Close $15,450.93.</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8215,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8223,12 +8225,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>WF Dec 2025 — no entity label</t>
+          <t>Verified SPLT INC acct 6813370423 (ending 0423) by PDF header. Dec 2025. Open $15,450.93 / Close $9,850.39.</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8252,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Personal-WF</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8260,12 +8262,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>WF Jan 2026 — probable SPLT 0423</t>
+          <t>ARIZE NWOSU / CHERYL L BENEFIELD personal WF checking 3725287282 (ending 7282). NOT in CLAUDE.md entity map — new finding. Jan 2026. Open $728.77 / Close $61.83. See OpenItems.</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8289,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8297,12 +8299,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>WF Jan 2026 alt copy</t>
+          <t>Verified SGM 8625 (6625678625). Jan 2026 CANONICAL. Open $492.38 / Close $1,609.62. Dup: S192.</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8326,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8334,12 +8336,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>WF Jan 2026 alt copy</t>
+          <t>Verified SPLT 0423 (6813370423). Jan 2026 CANONICAL. Open $9,850.39 / Close $8,049.38.</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8363,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8371,12 +8373,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>WF Jan 2026 alt copy</t>
+          <t>DUPLICATE of S190 (SGM Jan 2026). Verified SGM 8625. Identical balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8400,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8408,12 +8410,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>WF Feb 2026 — probable SPLT 0423</t>
+          <t>Verified SPLT 0423. Feb 2026 CANONICAL. Open $8,049.38 / Close $2,963.07.</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8437,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8445,12 +8447,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>WF Feb 2026 alt copy</t>
+          <t>Verified SGM 8625. Feb 2026 CANONICAL. Open $1,609.62 / Close -$24.18. Dup: S195.</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8474,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8482,12 +8484,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>WF Feb 2026 alt copy</t>
+          <t>DUPLICATE of S194 (SGM Feb 2026). Identical balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8511,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8519,12 +8521,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>WF Mar 2026</t>
+          <t>Verified SPLT 0423. Mar 2026 CANONICAL. Open $2,963.07 / Close $579.46.</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8548,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8556,12 +8558,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>WF Mar 2026 alt copy</t>
+          <t>Verified SGM 8625. Mar 2026 CANONICAL. Open -$24.18 / Close $677.01. Dup: S199.</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8585,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Personal-WF</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8593,12 +8595,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>WF Mar 2026 alt copy</t>
+          <t>ARIZE NWOSU / CHERYL L BENEFIELD personal WF 3725287282. Mar 2026. Close $422.72. See OpenItems.</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8622,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8630,12 +8632,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>WF Mar 2026 alt copy</t>
+          <t>DUPLICATE of S197 (SGM Mar 2026). Identical balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8659,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8667,12 +8669,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>WF Apr 2026</t>
+          <t>Verified SPLT 0423. Apr 2026 CANONICAL. Open $579.46 / Close $2,920.32.</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8696,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8704,12 +8706,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>WF Apr 2026 alt copy</t>
+          <t>Verified SGM 8625. Apr 2026 CANONICAL. Open $677.01 / Close $492.90. Dup: S202.</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8733,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8741,12 +8743,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>WF Apr 2026 alt copy</t>
+          <t>DUPLICATE of S201 (SGM Apr 2026). Identical balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8770,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8778,12 +8780,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>WF May 2026</t>
+          <t>Verified SPLT 0423. May 2026 CANONICAL. Open $2,920.32 / Close $3,571.86.</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8807,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8815,12 +8817,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>WF May 2026 alt copy</t>
+          <t>Verified SGM 8625. May 2026 CANONICAL. Open $492.90 / Close $2,945.78. Dup: S205.</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8844,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8852,12 +8854,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>WF May 2026 alt copy</t>
+          <t>DUPLICATE of S204 (SGM May 2026). Identical balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8881,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8889,12 +8891,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>WF Jun 2026</t>
+          <t>DUPLICATE of S207 (SPLT Jun 2026). Same account 6813370423, same opening balance $3,571.86.</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8918,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SPLT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8926,12 +8928,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>WF Jun 2026 alt copy</t>
+          <t>Verified SPLT 0423. Jun 2026 CANONICAL. Open $3,571.86 / Close: balance extraction failed — verify from PDF.</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8955,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SGM</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8963,12 +8965,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>WF Jun 2026 alt copy</t>
+          <t>Verified SGM 8625. Jun 2026 CANONICAL. Open $2,945.78 / Close $12,809.45.</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8992,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9000,12 +9002,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chase statement — entity unknown (personal credit card or SPLT Chase Ink?)</t>
+          <t>Acct XXXX XXXX XXXX 3247. Jul 2026. Prev bal $21,511.81 / New bal $22,055.63. Due 07/05/26. Billing cycle ~May-Jun 2026.</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9029,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9037,12 +9039,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chase statement 1 of 10</t>
+          <t>Acct XXXX XXXX XXXX 3247. Oct 2025. Prev bal $9,586.07 / New bal $15,005.21. Due 10/05/25. Billing cycle ~Aug-Sep 2025.</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9066,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9074,7 +9076,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. May 2025. Prev bal $0.00 / New bal $15,176.22. Due 05/05/25. Second cycle of new card. Billing cycle ~Mar-Apr 2025.</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9103,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9106,7 +9113,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Dec 2025. Prev bal $10,015.30 / New bal $15,573.71. Due 12/05/25. Billing cycle ~Oct-Nov 2025.</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9140,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9138,7 +9150,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Aug 2025. Prev bal $18,003.62 / New bal $8,437.20. Due 08/05/25. CANONICAL. Billing cycle ~Jun-Jul 2025. DUP: S217.</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9177,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9170,7 +9187,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Nov 2025. Prev bal $15,005.21 / New bal $10,015.30. Due 11/05/25. Billing cycle ~Sep-Oct 2025.</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9214,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9202,7 +9224,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Jun 2025. Prev bal $15,176.22 / New bal $10,713.54. Due 06/05/25. Billing cycle ~Apr-May 2025.</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9251,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9234,7 +9261,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Aug 2025. Prev bal $18,003.62 / New bal $8,437.20. DUPLICATE of S214. Same period, same balances confirmed.</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9288,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9266,7 +9298,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Mar 2025. Prev bal $0.00 / New bal $0.00. Due 04/05/25. FIRST statement. Period 02/09/25-03/08/25. New card, $0 balance. 60k bonus points + $31k purchases paid same cycle.</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9325,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9298,7 +9335,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Jan 2026. Prev bal $15,573.71 / New bal $12,817.71. Due 01/05/26. Billing cycle ~Nov-Dec 2025.</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9362,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Chase 3247</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9330,12 +9372,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>staged</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Chase statement 10 of 10</t>
+          <t>Acct XXXX XXXX XXXX 3247. Jul 2025. Prev bal $10,713.54 / New bal $18,003.62. Due 07/05/25. Billing cycle ~May-Jun 2025.</t>
         </is>
       </c>
     </row>
@@ -10446,6 +10488,43 @@
       <c r="G204" t="inlineStr">
         <is>
           <t>Kickstarter Proceeds Assignment memo — campaign under Cyberbrands, obligation and funds belong to SPLT; signed July 2026; ~$54,386 routed Cyberbrands-&gt;SPLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>S221</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Chase Sep 2025 (74F348C0)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>bank-stmt</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Chase-74F348C0-7E04-4F82-ACB2-99423FC4915C-list.pdf</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Acct XXXX XXXX XXXX 3247. Sep 2025. Prev bal $8,437.20 / New bal $9,586.07. Due 09/05/25. Billing cycle ~Jul-Aug 2025. File may be transaction list export (UUID in filename) rather than full statement PDF.</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10887,6 +10966,283 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Layer2.BankIndex</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BankIndex tab created (77 canonical entries)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Layer 2: Bank Statement Hygiene — built from account-number-verified PDF header extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S160-S163</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>entity=unknown</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>entity=SGM; status=verified</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Verified SGM 8625 (acct 6625678625) by PDF header for Sep-Dec 2023 statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S164-S175</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>entity=unknown</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>entity=Cyberbrands; status=duplicate</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Verified all 12 are Cyberbrands 5090 duplicates of S140-S151; identical balances confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S176</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>entity=unknown</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>entity=SGM; status=duplicate</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>013125 WellsFargo (1).pdf = SGM 8625, duplicate of S122</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S177-S188</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>entity=unknown</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>entity=SPLT; status=verified</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Verified SPLT 0423 (acct 6813370423) for all 12 months Jan-Dec 2025; balances extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S189</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>entity=unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>entity=Personal-WF; status=verified</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>013126 WellsFargo.pdf = ARIZE NWOSU personal acct 3725287282 — new finding</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S190-S208</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>entity=unknown</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>entity=SGM/SPLT/Personal-WF assigned; dups marked</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>All 2026 WF files assigned by account# from PDF; duplicates identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S210-S220</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>entity=unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>entity=Chase 3247; periods assigned; S217 marked dup</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Chase card verified as ending 3247; chronological order established; Chase7=dup of Chase4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Layer2.Sources.S221</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ADDED: Chase Sep 2025 (74F348C0 file) = Chase 3247 Jul-Aug 2025 cycle</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>New entry for previously unregistered Chase Sep 2025 statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Layer2.Finding.SPLT-open-date</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SPLT INC acct 6813370423 opened January 28 2025 per first statement (S177); $0 opening balance</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Confirms Jan 2025 entity formation; first statement covers only 3 days (Jan 28-31 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Layer2.Finding.Cyberbrands-entity-name</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cyberbrands 5090 held by CYBERBRANDS, LLC — NOT Social Gear Media LLC — confirmed from PDF header</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Entity name detection from transaction text is unreliable (SOCIAL GEAR MEDIA LLC appears in CB txn descriptions); account# is authoritative</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10898,7 +11254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -11284,6 +11640,161 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>v11 SGM_2025_Sales_Reconstruction shows $52,200 real sales with Jan ~$35,835 (100% Splitflask pre-SPLT-launch) and Feb-Dec winding down. Channels per v11: "Walmart.com/Macys.com" per tax filing. But SGM Amazon ($240K 1099-K) is separate. GMV $84,125 is an estimate. Needs: actual Walmart/Macy channel payout statements for SGM to confirm gross-of-fees revenue and validate $84,125 GMV estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SGM WF coverage gap: Jan-Aug 2023 (8 months)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>coverage-gap</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Layer 0 cash classification</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Oldest SGM statement on file is Sep 2023 (S160). SGM / Social Gear Media LLC was operating before that — at minimum 2022-2023. 8 months (Jan-Aug 2023) are missing. Obtain from WF to complete 2023 cash picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cyberbrands WF coverage gap: pre-2024 AND all of 2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>coverage-gap</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Layer 0 cash classification; COGS reconstruction</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cyberbrands 5090 statements on file: Jan-Dec 2024 only. No 2023 or earlier statements. No 2025 statements — but Cyberbrands filed $95,558 gross receipts in 2025 (Cyberbrands 2025 Schedule C). Obtain 2025 WF 5090 statements to reconstruct Cyberbrands 2025 cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chase 3247 coverage gap: Feb 2026 through Jun 2026 (5 missing cycles)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>coverage-gap</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Layer 0 cash classification; 2026 SPLT business expense reconstruction</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chase card ending 3247 statements on file: Mar 2025 first statement through Jan 2026 cycle, plus Jul 2026 cycle. Missing 5 billing cycles (Feb-Jun 2026). Gap in business expense tracking for H1 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Personal WF account 3725287282 (ending 7282) — not in CLAUDE.md entity map</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>investigate</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Entity attribution; founder personal vs business spend</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Found WF Everyday Checking account 3725287282 in name of ARIZE NWOSU / CHERYL L BENEFIELD. Files: S189 (Jan 2026), S198 (Mar 2026). Shows inbound transfers from SGM and Stripe (Social Gear Media branded). NOT in CLAUDE.md entity map. Determine: is this personal account or a sweep account? Also missing Feb/Apr/May/Jun 2026 statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SPLT Jun 2026 closing balance not extracted (S207)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>data-quality</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Balance extraction failed for SPLT Jun 2026 canonical (063026 WellsFargo (1).pdf / S207). Opening balance $3,571.86 confirmed. Read closing balance directly from PDF page 1-2 before Layer 3 cash classification.</t>
         </is>
       </c>
     </row>
@@ -11538,4 +12049,4267 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>period_label</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>canonical_file</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>canonical_sid</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>dup_count</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>dup_sids</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>opening_bal</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>closing_bal</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>account_type</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sep 2023</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>093023 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>S160</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>85.45</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>324.04</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>WF Business Checking</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2023 only Sep-Dec on file; Jan-Aug 2023 MISSING — see OpenItems</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Oct 2023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>103123 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>S161</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>324.04</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1,753.53</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>WF Business Checking</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nov 2023</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>113023 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>S162</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,753.53</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>729.26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>WF Business Checking</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dec 2023</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>123123 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>S163</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>729.26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>192.82</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>WF Business Checking</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Jan 2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SGM 013124 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S110</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>192.82</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>8,406.17</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Feb 2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SGM 022924 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S111</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,406.17</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>582.02</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SGM 033124 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S112</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>582.02</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>18,603.25</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Apr 2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SGM 043024 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S113</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18,603.25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>12,401.08</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>May 2024</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SGM 053124 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S114</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>12,401.08</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>503.11</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Jun 2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SGM 063024 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S115</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>503.11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3,553.76</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Jul 2024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SGM 073124 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S116</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,553.76</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>31,056.04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aug 2024</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SGM 083124 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S117</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>31,056.04</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4,122.92</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sep 2024</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SGM 093024 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S118</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4,122.92</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12,148.24</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Kangdao ambiguous wire in this month — see OpenItems</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Oct 2024</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SGM 103124 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S119</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>12,148.24</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7,142.86</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nov 2024</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SGM 113024 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S120</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7,142.86</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6,206.60</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dec 2024</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SGM 123124 WellsFargo (4).pdf</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6,206.60</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7,391.80</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Jan 2025</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SGM 013125 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>S176</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7,391.80</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2,540.97</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SGM 022825 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S123</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2,540.97</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>374.65</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SGM 033125 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S124</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>374.65</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>264.76</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SGM  043025 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S125</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>264.76</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-19.82</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Note: negative balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SGM 053125 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S126</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-19.82</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-14.42</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Negative balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SGM 063025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S127</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-14.42</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>19.92</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SGM 073125 WellsFargo (4).pdf</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>S128</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>19.92</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>43.90</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Very low balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SGM 083125 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>S129</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>43.90</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Very low balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SGM 093025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S130</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1,928.79</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SGM 103125 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S131</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1,928.79</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>35.46</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SGM 113025 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S132</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>35.46</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-16.55</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Negative balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D29" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SGM 123125 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S133</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-16.55</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>492.38</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>013126 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S190</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>S192</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>492.38</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1,609.62</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>022826 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S194</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>S195</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1,609.62</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-24.18</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Negative balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>033126 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S197</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>S199</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-24.18</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>677.01</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>043026 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S201</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>S202</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>677.01</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>492.90</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>053126 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S204</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>S205</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>492.90</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2,945.78</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6625678625</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>063026 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S208</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2,945.78</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>12,809.45</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>WF Navigate Business Checking</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Jan 2024</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>cyberbrands 013124 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S140</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>S164</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1,627.44</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>688.28</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>CYBERBRANDS, LLC per PDF header</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Feb 2024</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>cyberbrands 022924 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S141</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>S165</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>688.28</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>60.51</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>cyberbrands 033124 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S142</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>S166</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>60.51</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1,100.28</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Apr 2024</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>cyberbrands 043024 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S143</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>S167</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1,100.28</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2,473.33</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>May 2024</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>cyberbrands 053124 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S144</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>S168</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2,473.33</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>200.81</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Jun 2024</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>cyberbrands 063024 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S145</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>S169</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>200.81</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>206.90</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Jul 2024</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>cyberbrands 073124 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S146</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>S170</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>206.90</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>382.60</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aug 2024</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>cyberbrands 083124 WellsFargo (4).pdf</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S147</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>S171</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>382.60</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>580.88</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sep 2024</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>cyberbrands 093024 WellsFargo (5).pdf</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S148</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>S172</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>580.88</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>-5.76</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Negative balance Sep 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Oct 2024</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>cyberbrands 103124 WellsFargo (4).pdf</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S149</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>S173</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-5.76</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Opening inferred from Sep close</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D46" t="n">
+        <v>11</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Nov 2024</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>cyberbrands 113024 WellsFargo (5).pdf</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S150</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>S174</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>493.69</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D47" t="n">
+        <v>12</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Dec 2024</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>cyberbrands WellsFargo (6).pdf</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S151</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>S175</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>493.69</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>658.11</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Dec 2024 — unlabeled date filename but confirmed Dec 31 2024 per PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Jan 2025</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>013125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S177</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>693.00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Account OPENED Jan 28 2025. Period: Jan 28-31 only (3 days). Confirms SPLT formation date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>022825 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S178</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>693.00</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>5,125.15</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>033125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S179</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>5,125.15</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>7,501.24</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>043025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S180</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>7,501.24</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>13,285.66</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>053125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S181</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>13,285.66</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>91.04</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Large drawdown — large payment(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>063025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S182</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>91.04</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2,476.86</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D54" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>073125 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S183</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2,476.86</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>468.43</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>083125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S184</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>468.43</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2,279.21</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D56" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>093025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S185</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2,279.21</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>751.64</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>103125 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S186</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>751.64</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>4,628.21</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D58" t="n">
+        <v>11</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>113025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S187</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>4,628.21</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>15,450.93</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D59" t="n">
+        <v>12</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>123125 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S188</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>15,450.93</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>9,850.39</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>013126 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S191</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>9,850.39</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>8,049.38</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>022826 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S193</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>8,049.38</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2,963.07</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>033126 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S196</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2,963.07</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>579.46</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>043026 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S200</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>579.46</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2,920.32</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>053126 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S203</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2,920.32</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>3,571.86</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6813370423</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>063026 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S207</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>S206</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3,571.86</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Closing balance extraction failed — read directly from PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3725287282</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Personal-WF</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>013126 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S189</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>728.77</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>61.83</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>WF Everyday Checking (personal)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>ARIZE NWOSU/CHERYL L BENEFIELD personal acct. NOT in CLAUDE.md entity map. See OpenItems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3725287282</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Personal-WF</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>033126 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S198</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>422.72</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>WF Everyday Checking (personal)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Opening bal extraction failed — read from PDF. Missing: Feb/Apr/May/Jun 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Mar 2025 (cycle Feb9-Mar8)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Chase8.pdf</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S218</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>First statement. New card opened Feb 9 2025. $31k purchases fully paid. $550 annual fee. 60k bonus pts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>May 2025 (cycle Mar9-Apr8)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Chase2.pdf</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S212</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>15,176.22</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Second cycle. Rapid spend build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Jun 2025 (cycle Apr9-May8)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Chase6.pdf</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S216</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>15,176.22</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>10,713.54</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D71" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Jul 2025 (cycle May9-Jun8)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Chase10.pdf</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S220</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>10,713.54</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>18,003.62</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D72" t="n">
+        <v>7</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aug 2025 (cycle Jun9-Jul8)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Chase4.pdf</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S214</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>S217</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>18,003.62</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>8,437.20</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Sep 2025 (cycle Jul9-Aug8)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Chase-74F348C0-7E04-4F82-ACB2-99423FC4915C-list.pdf</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S221</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>8,437.20</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>9,586.07</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>UUID filename suggests downloaded list export; verify is full statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D74" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Oct 2025 (cycle Aug9-Sep8)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Chase1.pdf</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S211</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>9,586.07</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>15,005.21</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Nov 2025 (cycle Sep9-Oct8)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Chase5.pdf</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S215</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>15,005.21</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>10,015.30</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D76" t="n">
+        <v>11</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Dec 2025 (cycle Oct9-Nov8)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Chase3.pdf</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S213</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>10,015.30</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>15,573.71</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Jan 2026 (cycle Nov9-Dec8)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Chase9.pdf</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S219</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>15,573.71</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>12,817.71</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>MISSING: Feb-Jun 2026 cycles — see OpenItems</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D78" t="n">
+        <v>6</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Jul 2026 (cycle May9-Jun8)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Chase statement.pdf</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S210</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>21,511.81</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>22,055.63</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Gap: missing Feb-Jun 2026 cycles between this and Jan 2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Downloads/Splitflask-Financials/ledger.xlsx
+++ b/Downloads/Splitflask-Financials/ledger.xlsx
@@ -2931,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10528,6 +10528,746 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>S307</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Cyberbrands-013125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Cyberbrands-013125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Jan; WF 8025615090; open $658.11 → close $64.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>S308</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Cyberbrands-022825 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Cyberbrands-022825 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Feb; WF 8025615090; open $64.32 → close $118.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>S309</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Cyberbrands-033125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Cyberbrands-033125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Mar; WF 8025615090; open $118.01 → close $607.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>S310</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Cyberbrands-043025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Cyberbrands-043025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Apr; WF 8025615090; open $607.74 → close $29.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>S311</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Cyberbrands-053125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Cyberbrands-053125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 May; WF 8025615090; open $29.71 → close $260.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>S312</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Cyberbrands-063025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Cyberbrands-063025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Jun; WF 8025615090; open $260.60 → close $3.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>S313</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Cyberbrands-073125 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Cyberbrands-073125 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Jul; WF 8025615090; open $3.36 → close $6.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>S314</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Cyberbrands-083125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Cyberbrands-083125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Aug; WF 8025615090; open $6.15 → close $150.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>S315</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Cyberbrands-093025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Cyberbrands-093025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Sep; WF 8025615090; open $150.10 → close $88.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>S316</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Cyberbrands-103125 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Cyberbrands-103125 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Oct; WF 8025615090; open $88.76 → close $9.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>S317</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Cyberbrands-113025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Cyberbrands-113025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Nov; WF 8025615090; open $9.08 → close $177.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>S318</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Cyberbrands-123125 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Cyberbrands-123125 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Cyberbrands 2025 Dec; WF 8025615090; open $177.42 → close $1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>S319</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260108-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260108-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve; cycle Dec9-Jan8 2026; open $12,817.71 → close $15,637.55; payment due Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>S320</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260208-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260208-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve; cycle Jan9-Feb8 2026; open $15,637.55 → close $21,728.94; payment due Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>S321</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260308-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260308-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve; cycle Feb9-Mar8 2026; open $21,728.94 → close $21,963.59; payment due Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>S322</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260408-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260408-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve; cycle Mar9-Apr8 2026; open $21,963.59 → close $21,842.66; payment due May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>S323</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260508-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260508-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve; cycle Apr9-May8 2026; open $21,842.66 → close $21,511.81; payment due Jun 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>S324</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260608-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260608-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve; cycle May9-Jun8 2026; open $21,511.81 → close $22,055.63; payment due Jul 2026 — DUPLICATE of S210 (same cycle, different download)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>S325</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260708-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260708-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve; cycle Jun9-Jul8 2026; open $22,055.63 → close $22,659.65; payment due Aug 2026 — NEW beyond S210</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>S326</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-SPLT-INC-063026 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>bank_stmt</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-SPLT-INC-063026 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>staged</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>SPLT Jun 2026; WF 6813370423; open $3,571.86 → close $52.89; SUPERSEDES S207 (resolves failed closing balance extraction)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10539,7 +11279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11240,6 +11980,114 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>Entity name detection from transaction text is unreliable (SOCIAL GEAR MEDIA LLC appears in CB txn descriptions); account# is authoritative</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S207.closing_bal</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>52.89</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Layer 3 Step A: SPLT Jun 2026 closing balance resolved via new superseding file 2026-SPLT-INC-063026 WellsFargo.pdf (S326)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BankIndex.Cyberbrands.2025</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>missing (12 months)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>S307-S318 added</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Layer 3 Step A: 12 Cyberbrands 2025 monthly statements indexed (Jan-Dec 2025; WF 8025615090). Opens at $658.11 (= S151 Dec2024 close ✓). Resolves CLAUDE.md open item re: missing 2025 Cyberbrands stmts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BankIndex.Chase.2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>gap (Feb-Jun 2026 missing)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>S319-S325 added</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Layer 3 Step A: 7 Chase Sapphire Reserve 2026 cycles indexed. Fill gap between S219 (Jan2026) and S210 (May-Jun2026). S324 = dup of S210 (same cycle). S325 = new beyond S210 (Jun9-Jul8, close $22,659.65).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S210.dup_count</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Layer 3 Step A: S210 dup_sids updated to S324 (the 20260608 download is the same May9-Jun8 2026 cycle)</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12233,7 +13081,6 @@
           <t>WF Business Checking</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12285,7 +13132,6 @@
           <t>WF Business Checking</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12337,7 +13183,6 @@
           <t>WF Business Checking</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12389,7 +13234,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12441,7 +13285,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12493,7 +13336,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12545,7 +13387,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12597,7 +13438,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12649,7 +13489,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12701,7 +13540,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12753,7 +13591,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12861,7 +13698,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12913,7 +13749,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12965,7 +13800,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13022,7 +13856,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13074,7 +13907,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13126,7 +13958,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13290,7 +14121,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13454,7 +14284,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13506,7 +14335,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13614,7 +14442,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13671,7 +14498,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13789,7 +14615,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13846,7 +14671,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13903,7 +14727,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13955,7 +14778,6 @@
           <t>WF Navigate Business Checking</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14073,7 +14895,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -14130,7 +14951,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14187,7 +15007,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14244,7 +15063,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14301,7 +15119,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14358,7 +15175,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14415,7 +15231,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14594,7 +15409,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14763,7 +15577,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14815,7 +15628,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14867,7 +15679,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -14975,7 +15786,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15027,7 +15837,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15079,7 +15888,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15131,7 +15939,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15183,7 +15990,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15235,7 +16041,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15287,7 +16092,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15339,7 +16143,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15391,7 +16194,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15443,7 +16245,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -15495,7 +16296,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -15547,7 +16347,6 @@
           <t>WF Initiate Business Checking</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15594,6 +16393,11 @@
           <t>3,571.86</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>52.89</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>WF Initiate Business Checking</t>
@@ -15601,7 +16405,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Closing balance extraction failed — read directly from PDF</t>
+          <t>Closing balance $52.89 resolved via 2026-SPLT-INC-063026 WellsFargo.pdf (S326)</t>
         </is>
       </c>
     </row>
@@ -15874,7 +16678,6 @@
           <t>Chase Sapphire Reserve (credit card)</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15926,7 +16729,6 @@
           <t>Chase Sapphire Reserve (credit card)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15983,7 +16785,6 @@
           <t>Chase Sapphire Reserve (credit card)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16091,7 +16892,6 @@
           <t>Chase Sapphire Reserve (credit card)</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -16143,7 +16943,6 @@
           <t>Chase Sapphire Reserve (credit card)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -16195,7 +16994,6 @@
           <t>Chase Sapphire Reserve (credit card)</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -16286,26 +17084,1030 @@
         </is>
       </c>
       <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>S324</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>21,511.81</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>22,055.63</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Canonical for cycle May9-Jun8 2026. Duplicate file added as S324 (20260608 download). Both confirm open $21,511.81 → close $22,055.63.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Jan 2025</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Cyberbrands-013125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S307</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>658.11</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>64.32</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Resolves CLAUDE.md open item: Cyberbrands 2025 stmts now on file. Opening $658.11 ties to Dec 2024 S151 closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Cyberbrands-022825 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S308</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>64.32</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>118.01</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Cyberbrands-033125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S309</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>118.01</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>607.74</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Cyberbrands-043025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S310</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>607.74</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>29.71</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D83" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Cyberbrands-053125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S311</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>29.71</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>260.60</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D84" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Cyberbrands-063025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S312</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>260.60</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D85" t="n">
+        <v>7</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Cyberbrands-073125 WellsFargo (3).pdf</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S313</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Cyberbrands-083125 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S314</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>150.10</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Cyberbrands-093025 WellsFargo.pdf</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S315</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>150.10</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>88.76</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Cyberbrands-103125 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S316</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>88.76</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>9.08</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D89" t="n">
+        <v>11</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Cyberbrands-113025 WellsFargo (1).pdf</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S317</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>9.08</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>177.42</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>8025615090</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cyberbrands</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D90" t="n">
+        <v>12</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Cyberbrands-123125 WellsFargo (2).pdf</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S318</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>177.42</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>WF Initiate Business Checking</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Dec 2025 closing $1.50; effectively wound down</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Feb 2026 (cycle Dec9-Jan8)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260108-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S319</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>12,817.71</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>15,637.55</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Fills gap between S219 (Jan2026) and S210 (May9-Jun8). Opening $12,817.71 ties to S219 closing ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Mar 2026 (cycle Jan9-Feb8)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260208-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S320</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>15,637.55</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>21,728.94</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Apr 2026 (cycle Feb9-Mar8)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260308-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S321</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>21,728.94</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>21,963.59</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D94" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>May 2026 (cycle Mar9-Apr8)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260408-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S322</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>21,963.59</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>21,842.66</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D95" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Jun 2026 (cycle Apr9-May8)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260508-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S323</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>21,842.66</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>21,511.81</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Jul 2026 (cycle May9-Jun8)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260608-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S324</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>S210</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>21,511.81</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>22,055.63</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>Chase Sapphire Reserve (credit card)</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Gap: missing Feb-Jun 2026 cycles between this and Jan 2026</t>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>DUPLICATE of S210 (same cycle May9-Jun8; different download filename). Both agree on balances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>xxxx-3247</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Chase 3247</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D97" t="n">
+        <v>7</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aug 2026 (cycle Jun9-Jul8)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026 Chase Creditcard Statements-20260708-statements-3247-.pdf</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S325</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>22,055.63</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>22,659.65</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve (credit card)</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>NEW coverage beyond S210. Opening $22,055.63 = S210 closing ✓</t>
         </is>
       </c>
     </row>

--- a/Downloads/Splitflask-Financials/ledger.xlsx
+++ b/Downloads/Splitflask-Financials/ledger.xlsx
@@ -12385,7 +12385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13319,6 +13319,141 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>Amounts corrected to actual: $13152.36-&gt;$12.98, $25051.28-&gt;$9.99, $18438.69-&gt;$0.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SGM_2024_Txns:ALL_DEBIT_MONTHS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>multiple inflated amounts (running balance captured as debit)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>77 debit rows corrected to actual transaction amounts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Parser artifact sweep: two-amount lines had last amount (running balance) stored; replaced with first amount (actual debit). Correction map built from raw PDF text for all 12 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SGM_2024_Txns:2024/03/3/29</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BANK_FEE $25.00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ADDED by reconciliation: row was never captured by original extractor (extractor stored closing balance $18,603.25 as phantom; correction removed phantom but did not create $25 fee row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SGM_2024_Txns:2024/07/7/31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BANK_FEE $25.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ADDED by reconciliation: same pattern — extractor captured closing balance $31,056.04 as phantom; correction removed phantom but fee row was missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SGM_2024_Txns:2024/09/9/17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DEBT_SBA_EIDL $2018.00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ADDED by reconciliation: SBA EIDL row was never captured. PDF shows 2,018.00 27,244.45; phantom $27,244.45 was not in ledger so correction did not trigger; row simply missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Figures:sgm.2024.deduct.*</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pre-reconciliation totals</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>post-reconciliation totals (77 artifact corrections + 3 missing rows added)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>All 12 SGM 2024 months now foot to penny. Deduction totals recomputed from verified transaction set.</t>
         </is>
       </c>
     </row>
@@ -19687,7 +19822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2023"/>
+  <dimension ref="A1:H2026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21814,7 +21949,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12417.66</v>
+        <v>7.92</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -21829,6 +21964,11 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>S110</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12417.66→7.92 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -22199,7 +22339,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12855.24</v>
+        <v>122.41</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -22214,6 +22354,11 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>S110</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12855.24→122.41 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22449,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12984.61</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -22319,6 +22464,11 @@
       <c r="G75" t="inlineStr">
         <is>
           <t>S110</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12984.61→9.97 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -24374,7 +24524,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11676.04</v>
+        <v>3000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -24389,6 +24539,11 @@
       <c r="G134" t="inlineStr">
         <is>
           <t>S111</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11676.04→3000.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -24444,7 +24599,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11929.25</v>
+        <v>82.13</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -24459,6 +24614,11 @@
       <c r="G136" t="inlineStr">
         <is>
           <t>S111</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11929.25→82.13 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25199,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10069.47</v>
+        <v>700</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -25054,6 +25214,11 @@
       <c r="G153" t="inlineStr">
         <is>
           <t>S111</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10069.47→700.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -31024,7 +31189,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>11307.53</v>
+        <v>500</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -31039,6 +31204,11 @@
       <c r="G324" t="inlineStr">
         <is>
           <t>S112</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11307.53→500.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -31094,7 +31264,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>11547.04</v>
+        <v>55.25</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -31109,6 +31279,11 @@
       <c r="G326" t="inlineStr">
         <is>
           <t>S112</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11547.04→55.25 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -31759,7 +31934,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>19043.77</v>
+        <v>38.6</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -31774,6 +31949,11 @@
       <c r="G345" t="inlineStr">
         <is>
           <t>S112</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 19043.77→38.60 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -32074,7 +32254,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>18634.06</v>
+        <v>300</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -32089,6 +32269,11 @@
       <c r="G354" t="inlineStr">
         <is>
           <t>S112</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 18634.06→300.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -32354,7 +32539,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>18478.91</v>
+        <v>60.96</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -32369,6 +32554,11 @@
       <c r="G362" t="inlineStr">
         <is>
           <t>S112</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 18478.91→60.96 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32649,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>18610.5</v>
+        <v>125.58</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -32474,6 +32664,11 @@
       <c r="G365" t="inlineStr">
         <is>
           <t>S112</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 18610.50→125.58 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -33089,7 +33284,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>10340.27</v>
+        <v>1000</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -33104,6 +33299,11 @@
       <c r="G383" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10340.27→1000.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -33474,7 +33674,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>10700.17</v>
+        <v>25.78</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -33489,6 +33689,11 @@
       <c r="G394" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10700.17→25.78 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34799,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>12309.5</v>
+        <v>2378.44</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -34609,6 +34814,11 @@
       <c r="G426" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12309.50→2378.44 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -34839,7 +35049,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>12844.32</v>
+        <v>202</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -34854,6 +35064,11 @@
       <c r="G433" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12844.32→202.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -34979,7 +35194,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>13365.24</v>
+        <v>60.98</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -34994,6 +35209,11 @@
       <c r="G437" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 13365.24→60.98 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -35154,7 +35374,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>42417.42</v>
+        <v>25.89</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -35169,6 +35389,11 @@
       <c r="G442" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 42417.42→25.89 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -35364,7 +35589,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>25067.47</v>
+        <v>136.75</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -35379,6 +35604,11 @@
       <c r="G448" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 25067.47→136.75 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -35579,7 +35809,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>25436.17</v>
+        <v>100</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -35594,6 +35824,11 @@
       <c r="G454" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 25436.17→100.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -35859,7 +36094,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>23583.99</v>
+        <v>100</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -35874,6 +36109,11 @@
       <c r="G462" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 23583.99→100.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -36209,7 +36449,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>21242.89</v>
+        <v>127.24</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -36224,6 +36464,11 @@
       <c r="G472" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 21242.89→127.24 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -36454,7 +36699,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>19734.92</v>
+        <v>915.53</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -36469,6 +36714,11 @@
       <c r="G479" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 19734.92→915.53 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -36839,7 +37089,7 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>16514.96</v>
+        <v>406.35</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -36854,6 +37104,11 @@
       <c r="G490" t="inlineStr">
         <is>
           <t>S113</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 16514.96→406.35 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -37609,7 +37864,7 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>29614.61</v>
+        <v>35</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
@@ -37624,6 +37879,11 @@
       <c r="G512" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 29614.61→35.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -37854,7 +38114,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>28707.4</v>
+        <v>35</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -37869,6 +38129,11 @@
       <c r="G519" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 28707.40→35.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -38064,7 +38329,7 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>31748.99</v>
+        <v>22.78</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -38079,6 +38344,11 @@
       <c r="G525" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 31748.99→22.78 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -39079,7 +39349,7 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>12803.34</v>
+        <v>2000</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -39094,6 +39364,11 @@
       <c r="G554" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12803.34→2000.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39599,7 @@
         </is>
       </c>
       <c r="D561" t="n">
-        <v>12080.17</v>
+        <v>2227.65</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
@@ -39339,6 +39614,11 @@
       <c r="G561" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12080.17→2227.65 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -39569,7 +39849,7 @@
         </is>
       </c>
       <c r="D568" t="n">
-        <v>24022.3</v>
+        <v>187.46</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
@@ -39584,6 +39864,11 @@
       <c r="G568" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 24022.30→187.46 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -39744,7 +40029,7 @@
         </is>
       </c>
       <c r="D573" t="n">
-        <v>47868.21</v>
+        <v>40.95</v>
       </c>
       <c r="E573" t="inlineStr">
         <is>
@@ -39759,6 +40044,11 @@
       <c r="G573" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 47868.21→40.95 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -40409,7 +40699,7 @@
         </is>
       </c>
       <c r="D592" t="n">
-        <v>10393.38</v>
+        <v>409</v>
       </c>
       <c r="E592" t="inlineStr">
         <is>
@@ -40424,6 +40714,11 @@
       <c r="G592" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10393.38→409.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -40549,7 +40844,7 @@
         </is>
       </c>
       <c r="D596" t="n">
-        <v>11026.81</v>
+        <v>2305</v>
       </c>
       <c r="E596" t="inlineStr">
         <is>
@@ -40564,6 +40859,11 @@
       <c r="G596" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11026.81→2305.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -40794,7 +41094,7 @@
         </is>
       </c>
       <c r="D603" t="n">
-        <v>11552.01</v>
+        <v>83.42</v>
       </c>
       <c r="E603" t="inlineStr">
         <is>
@@ -40809,6 +41109,11 @@
       <c r="G603" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11552.01→83.42 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -40969,7 +41274,7 @@
         </is>
       </c>
       <c r="D608" t="n">
-        <v>11317.49</v>
+        <v>900</v>
       </c>
       <c r="E608" t="inlineStr">
         <is>
@@ -40984,6 +41289,11 @@
       <c r="G608" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11317.49→900.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -41529,7 +41839,7 @@
         </is>
       </c>
       <c r="D624" t="n">
-        <v>10358.69</v>
+        <v>2500</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
@@ -41544,6 +41854,11 @@
       <c r="G624" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10358.69→2500.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -41844,7 +42159,7 @@
         </is>
       </c>
       <c r="D633" t="n">
-        <v>13952.58</v>
+        <v>202</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
@@ -41859,6 +42174,11 @@
       <c r="G633" t="inlineStr">
         <is>
           <t>S114</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 13952.58→202.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -45589,7 +45909,7 @@
         </is>
       </c>
       <c r="D740" t="n">
-        <v>12466.95</v>
+        <v>2509.82</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
@@ -45604,6 +45924,11 @@
       <c r="G740" t="inlineStr">
         <is>
           <t>S115</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12466.95→2509.82 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -49544,7 +49869,7 @@
         </is>
       </c>
       <c r="D853" t="n">
-        <v>12421.6</v>
+        <v>49.95</v>
       </c>
       <c r="E853" t="inlineStr">
         <is>
@@ -49559,6 +49884,11 @@
       <c r="G853" t="inlineStr">
         <is>
           <t>S116</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12421.60→49.95 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -52169,7 +52499,7 @@
         </is>
       </c>
       <c r="D928" t="n">
-        <v>10861.29</v>
+        <v>2018</v>
       </c>
       <c r="E928" t="inlineStr">
         <is>
@@ -52184,6 +52514,11 @@
       <c r="G928" t="inlineStr">
         <is>
           <t>S116</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10861.29→2018.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -52449,7 +52784,7 @@
         </is>
       </c>
       <c r="D936" t="n">
-        <v>11380.59</v>
+        <v>105.5</v>
       </c>
       <c r="E936" t="inlineStr">
         <is>
@@ -52464,6 +52799,11 @@
       <c r="G936" t="inlineStr">
         <is>
           <t>S116</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11380.59→105.50 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -52694,7 +53034,7 @@
         </is>
       </c>
       <c r="D943" t="n">
-        <v>22717.98</v>
+        <v>55.75</v>
       </c>
       <c r="E943" t="inlineStr">
         <is>
@@ -52709,6 +53049,11 @@
       <c r="G943" t="inlineStr">
         <is>
           <t>S116</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 22717.98→55.75 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -55074,7 +55419,7 @@
         </is>
       </c>
       <c r="D1011" t="n">
-        <v>31240.39</v>
+        <v>66.3</v>
       </c>
       <c r="E1011" t="inlineStr">
         <is>
@@ -55089,6 +55434,11 @@
       <c r="G1011" t="inlineStr">
         <is>
           <t>S116</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 31240.39→66.30 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -55669,7 +56019,7 @@
         </is>
       </c>
       <c r="D1028" t="n">
-        <v>27851.52</v>
+        <v>3000</v>
       </c>
       <c r="E1028" t="inlineStr">
         <is>
@@ -55684,6 +56034,11 @@
       <c r="G1028" t="inlineStr">
         <is>
           <t>S117</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 27851.52→3000.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -55949,7 +56304,7 @@
         </is>
       </c>
       <c r="D1036" t="n">
-        <v>31075.71</v>
+        <v>612.49</v>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
@@ -55964,6 +56319,11 @@
       <c r="G1036" t="inlineStr">
         <is>
           <t>S117</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 31075.71→612.49 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -56194,7 +56554,7 @@
         </is>
       </c>
       <c r="D1043" t="n">
-        <v>35981.01</v>
+        <v>105.5</v>
       </c>
       <c r="E1043" t="inlineStr">
         <is>
@@ -56209,6 +56569,11 @@
       <c r="G1043" t="inlineStr">
         <is>
           <t>S117</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 35981.01→105.50 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -56474,7 +56839,7 @@
         </is>
       </c>
       <c r="D1051" t="n">
-        <v>35644.36</v>
+        <v>137.15</v>
       </c>
       <c r="E1051" t="inlineStr">
         <is>
@@ -56489,6 +56854,11 @@
       <c r="G1051" t="inlineStr">
         <is>
           <t>S117</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 35644.36→137.15 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -62534,7 +62904,7 @@
         </is>
       </c>
       <c r="D1224" t="n">
-        <v>25752.21</v>
+        <v>400</v>
       </c>
       <c r="E1224" t="inlineStr">
         <is>
@@ -62549,6 +62919,11 @@
       <c r="G1224" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 25752.21→400.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -62814,7 +63189,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>20748.45</v>
+        <v>147.6</v>
       </c>
       <c r="E1232" t="inlineStr">
         <is>
@@ -62829,6 +63204,11 @@
       <c r="G1232" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 20748.45→147.60 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -63129,7 +63509,7 @@
         </is>
       </c>
       <c r="D1241" t="n">
-        <v>24022.33</v>
+        <v>105.5</v>
       </c>
       <c r="E1241" t="inlineStr">
         <is>
@@ -63144,6 +63524,11 @@
       <c r="G1241" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 24022.33→105.50 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -63269,7 +63654,7 @@
         </is>
       </c>
       <c r="D1245" t="n">
-        <v>23853.85</v>
+        <v>200</v>
       </c>
       <c r="E1245" t="inlineStr">
         <is>
@@ -63284,6 +63669,11 @@
       <c r="G1245" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 23853.85→200.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -63584,7 +63974,7 @@
         </is>
       </c>
       <c r="D1254" t="n">
-        <v>21939.32</v>
+        <v>5000</v>
       </c>
       <c r="E1254" t="inlineStr">
         <is>
@@ -63599,6 +63989,11 @@
       <c r="G1254" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 21939.32→5000.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -63934,7 +64329,7 @@
         </is>
       </c>
       <c r="D1264" t="n">
-        <v>23669.77</v>
+        <v>2291.34</v>
       </c>
       <c r="E1264" t="inlineStr">
         <is>
@@ -63949,6 +64344,11 @@
       <c r="G1264" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 23669.77→2291.34 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -64424,7 +64824,7 @@
         </is>
       </c>
       <c r="D1278" t="n">
-        <v>14714.77</v>
+        <v>15000</v>
       </c>
       <c r="E1278" t="inlineStr">
         <is>
@@ -64439,6 +64839,11 @@
       <c r="G1278" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 14714.77→15000.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -64564,7 +64969,7 @@
         </is>
       </c>
       <c r="D1282" t="n">
-        <v>16686.74</v>
+        <v>193.3</v>
       </c>
       <c r="E1282" t="inlineStr">
         <is>
@@ -64579,6 +64984,11 @@
       <c r="G1282" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 16686.74→193.30 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -65964,7 +66374,7 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>11671.24</v>
+        <v>233.96</v>
       </c>
       <c r="E1322" t="inlineStr">
         <is>
@@ -65979,6 +66389,11 @@
       <c r="G1322" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11671.24→233.96 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -66874,7 +67289,7 @@
         </is>
       </c>
       <c r="D1348" t="n">
-        <v>12148.24</v>
+        <v>25</v>
       </c>
       <c r="E1348" t="inlineStr">
         <is>
@@ -66889,6 +67304,11 @@
       <c r="G1348" t="inlineStr">
         <is>
           <t>S118</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12148.24→25.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -67294,7 +67714,7 @@
         </is>
       </c>
       <c r="D1360" t="n">
-        <v>14076.36</v>
+        <v>200</v>
       </c>
       <c r="E1360" t="inlineStr">
         <is>
@@ -67309,6 +67729,11 @@
       <c r="G1360" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 14076.36→200.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -67574,7 +67999,7 @@
         </is>
       </c>
       <c r="D1368" t="n">
-        <v>11162.42</v>
+        <v>583.3200000000001</v>
       </c>
       <c r="E1368" t="inlineStr">
         <is>
@@ -67589,6 +68014,11 @@
       <c r="G1368" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11162.42→583.32 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -67854,7 +68284,7 @@
         </is>
       </c>
       <c r="D1376" t="n">
-        <v>12556.68</v>
+        <v>300</v>
       </c>
       <c r="E1376" t="inlineStr">
         <is>
@@ -67869,6 +68299,11 @@
       <c r="G1376" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12556.68→300.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -69079,7 +69514,7 @@
         </is>
       </c>
       <c r="D1411" t="n">
-        <v>11896.25</v>
+        <v>1235</v>
       </c>
       <c r="E1411" t="inlineStr">
         <is>
@@ -69094,6 +69529,11 @@
       <c r="G1411" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11896.25→1235.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -69219,7 +69659,7 @@
         </is>
       </c>
       <c r="D1415" t="n">
-        <v>12684.32</v>
+        <v>500</v>
       </c>
       <c r="E1415" t="inlineStr">
         <is>
@@ -69234,6 +69674,11 @@
       <c r="G1415" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12684.32→500.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -69429,7 +69874,7 @@
         </is>
       </c>
       <c r="D1421" t="n">
-        <v>13373.04</v>
+        <v>55.75</v>
       </c>
       <c r="E1421" t="inlineStr">
         <is>
@@ -69444,6 +69889,11 @@
       <c r="G1421" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 13373.04→55.75 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -69639,7 +70089,7 @@
         </is>
       </c>
       <c r="D1427" t="n">
-        <v>12813.61</v>
+        <v>201.04</v>
       </c>
       <c r="E1427" t="inlineStr">
         <is>
@@ -69654,6 +70104,11 @@
       <c r="G1427" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12813.61→201.04 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -70689,7 +71144,7 @@
         </is>
       </c>
       <c r="D1457" t="n">
-        <v>10336.62</v>
+        <v>200</v>
       </c>
       <c r="E1457" t="inlineStr">
         <is>
@@ -70704,6 +71159,11 @@
       <c r="G1457" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10336.62→200.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -70934,7 +71394,7 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>11615.59</v>
+        <v>10.38</v>
       </c>
       <c r="E1464" t="inlineStr">
         <is>
@@ -70949,6 +71409,11 @@
       <c r="G1464" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11615.59→10.38 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -71039,7 +71504,7 @@
         </is>
       </c>
       <c r="D1467" t="n">
-        <v>11892.95</v>
+        <v>200</v>
       </c>
       <c r="E1467" t="inlineStr">
         <is>
@@ -71054,6 +71519,11 @@
       <c r="G1467" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11892.95→200.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -71284,7 +71754,7 @@
         </is>
       </c>
       <c r="D1474" t="n">
-        <v>11086.87</v>
+        <v>168.8</v>
       </c>
       <c r="E1474" t="inlineStr">
         <is>
@@ -71299,6 +71769,11 @@
       <c r="G1474" t="inlineStr">
         <is>
           <t>S119</t>
+        </is>
+      </c>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 11086.87→168.80 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -84199,7 +84674,7 @@
         </is>
       </c>
       <c r="D1843" t="n">
-        <v>10153.11</v>
+        <v>35</v>
       </c>
       <c r="E1843" t="inlineStr">
         <is>
@@ -84214,6 +84689,11 @@
       <c r="G1843" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1843" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10153.11→35.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -84794,7 +85274,7 @@
         </is>
       </c>
       <c r="D1860" t="n">
-        <v>13619.91</v>
+        <v>65</v>
       </c>
       <c r="E1860" t="inlineStr">
         <is>
@@ -84809,6 +85289,11 @@
       <c r="G1860" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1860" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 13619.91→65.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -86859,7 +87344,7 @@
         </is>
       </c>
       <c r="D1919" t="n">
-        <v>12812.71</v>
+        <v>20.14</v>
       </c>
       <c r="E1919" t="inlineStr">
         <is>
@@ -86874,6 +87359,11 @@
       <c r="G1919" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1919" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 12812.71→20.14 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -87069,7 +87559,7 @@
         </is>
       </c>
       <c r="D1925" t="n">
-        <v>20438.2</v>
+        <v>15</v>
       </c>
       <c r="E1925" t="inlineStr">
         <is>
@@ -87084,6 +87574,11 @@
       <c r="G1925" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1925" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 20438.20→15.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -87489,7 +87984,7 @@
         </is>
       </c>
       <c r="D1937" t="n">
-        <v>26667.55</v>
+        <v>55.75</v>
       </c>
       <c r="E1937" t="inlineStr">
         <is>
@@ -87504,6 +87999,11 @@
       <c r="G1937" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1937" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 26667.55→55.75 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -88049,7 +88549,7 @@
         </is>
       </c>
       <c r="D1953" t="n">
-        <v>24860.56</v>
+        <v>66.3</v>
       </c>
       <c r="E1953" t="inlineStr">
         <is>
@@ -88064,6 +88564,11 @@
       <c r="G1953" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1953" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 24860.56→66.30 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -88609,7 +89114,7 @@
         </is>
       </c>
       <c r="D1969" t="n">
-        <v>30387.59</v>
+        <v>35</v>
       </c>
       <c r="E1969" t="inlineStr">
         <is>
@@ -88624,6 +89129,11 @@
       <c r="G1969" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1969" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 30387.59→35.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -88959,7 +89469,7 @@
         </is>
       </c>
       <c r="D1979" t="n">
-        <v>10369.34</v>
+        <v>35</v>
       </c>
       <c r="E1979" t="inlineStr">
         <is>
@@ -88974,6 +89484,11 @@
       <c r="G1979" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H1979" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 10369.34→35.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -90009,7 +90524,7 @@
         </is>
       </c>
       <c r="D2009" t="n">
-        <v>15287.59</v>
+        <v>65</v>
       </c>
       <c r="E2009" t="inlineStr">
         <is>
@@ -90024,6 +90539,11 @@
       <c r="G2009" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+      <c r="H2009" t="inlineStr">
+        <is>
+          <t>ARTIFACT CORRECTED: 15287.59→65.00 (was running balance)</t>
         </is>
       </c>
     </row>
@@ -90514,6 +91034,126 @@
       <c r="G2023" t="inlineStr">
         <is>
           <t>S121</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2024/03/3/29</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>debit</t>
+        </is>
+      </c>
+      <c r="D2024" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>BANK_FEE</t>
+        </is>
+      </c>
+      <c r="F2024" t="inlineStr">
+        <is>
+          <t>Monthly Service Fee</t>
+        </is>
+      </c>
+      <c r="G2024" t="inlineStr">
+        <is>
+          <t>S112</t>
+        </is>
+      </c>
+      <c r="H2024" t="inlineStr">
+        <is>
+          <t>ADDED by reconciliation: row was never captured by original extractor (extractor stored closing balance $18,603.25 as phantom; correction removed phantom but did not create $25 fee row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2024/07/7/31</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>debit</t>
+        </is>
+      </c>
+      <c r="D2025" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>BANK_FEE</t>
+        </is>
+      </c>
+      <c r="F2025" t="inlineStr">
+        <is>
+          <t>Monthly Service Fee</t>
+        </is>
+      </c>
+      <c r="G2025" t="inlineStr">
+        <is>
+          <t>S116</t>
+        </is>
+      </c>
+      <c r="H2025" t="inlineStr">
+        <is>
+          <t>ADDED by reconciliation: same pattern — extractor captured closing balance $31,056.04 as phantom; correction removed phantom but fee row was missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2024/09/9/17</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>debit</t>
+        </is>
+      </c>
+      <c r="D2026" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>DEBT_SBA_EIDL</t>
+        </is>
+      </c>
+      <c r="F2026" t="inlineStr">
+        <is>
+          <t>&lt; Business to Business ACH Debit - Sba Eidl Loan Payment 240916</t>
+        </is>
+      </c>
+      <c r="G2026" t="inlineStr">
+        <is>
+          <t>S118</t>
+        </is>
+      </c>
+      <c r="H2026" t="inlineStr">
+        <is>
+          <t>ADDED by reconciliation: SBA EIDL row was never captured. PDF shows 2,018.00 27,244.45; phantom $27,244.45 was not in ledger so correction did not trigger; row simply missing</t>
         </is>
       </c>
     </row>

--- a/Downloads/Splitflask-Financials/ledger.xlsx
+++ b/Downloads/Splitflask-Financials/ledger.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>All confirmed as international distributor/wholesale wire payments into SPLT WF 0423. NOT inside Amazon/Shopify platform totals (separate wire channel). Named international customers = separate B2B channel. Double-count risk low (wires vs platform settlements are distinct bank credits).</t>
+          <t>All confirmed as international distributor/wholesale wire payments into SPLT WF 0423. NOT inside Amazon/Shopify platform totals (separate wire channel). Named international customers = separate B2B channel. Double-count risk low (wires vs platform settlements are distinct bank credits). | Layer 1 recon 2026-07-09: Artifact check CLEAN. All 5 wire amounts (Kuwait $1,410.21, EK AU $1,529.83, Waen JP $1,742.31, Citiesocial TW $1,029.58, Citiesocial TW $1,974.31) are plausible within their respective monthly SPLT net flows and are far below any monthly SPLT balance. Balance chain unbroken S177-S188. Wire amounts are in the typical range for B2B international distributor wires and do NOT match any running balance. Status provisional — would require specific wire line-item verification against SPLT 2025 statements to reach locked.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>OPEN_SGM_2025_reconciliation: filed $130,976 = raw bank-feed deposits; $52,200 = stripped of loans/intercompany/refunds/Teslarati. GMV $84,125 is an ESTIMATE (gross-of-fees haircut applied to $52,200 net). Cannot be independently verified from available documents — needs bank classification to separate actual gross sales from net and from deposits. SGM 2025 filed loss -$32,900 per 1120-S.</t>
+          <t>OPEN_SGM_2025_reconciliation: filed $130,976 = raw bank-feed deposits; $52,200 = stripped of loans/intercompany/refunds/Teslarati. GMV $84,125 is an ESTIMATE (gross-of-fees haircut applied to $52,200 net). Cannot be independently verified from available documents — needs bank classification to separate actual gross sales from net and from deposits. SGM 2025 filed loss -$32,900 per 1120-S. | Layer 1 recon 2026-07-09: Artifact check N/A — this is a FORMULA ESTIMATE (gross-of-fees uplift applied to $52,200 net), not a direct bank read. No parser artifact possible in a formula. Status unchanged provisional-estimate; not eligible for V12 until actual wholesale gross revenue is sourced from Walmart/Macy channel payouts or invoices.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Jan 2025 ~$35,835 (SGM had 100% of Splitflask revenue Jan before SPLT launched Feb 2025); Feb-Dec winding down intl/wholesale residual. Net basis only; GMV gross figure is estimated ($84,125).</t>
+          <t>Jan 2025 ~$35,835 (SGM had 100% of Splitflask revenue Jan before SPLT launched Feb 2025); Feb-Dec winding down intl/wholesale residual. Net basis only; GMV gross figure is estimated ($84,125). | Layer 1 recon 2026-07-09: Artifact check CLEAN. $52,200 &gt;&gt; max SGM 2025 balance ($7,391.80) — cannot be a balance artifact. The underlying total $130,976 is now provisional-footed (see sgm.2025.gross_receipts). The $52,200 itself is a CLASSIFICATION result (stripping $78,776 non-revenue from $130,976): loans/intercompany/refunds/Teslarati identified by transaction description, not by bank-PDF parse of amounts. No parser artifact affects classification labels. Status remains provisional because individual statement transaction extraction (SGM_2025_Txns) has not been run; the classification is from v11 SGM_2025_Sales_Reconstruction. V12 eligibility: eligible once CPA confirms classification of the $78,776 excluded non-revenue items.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional-footed</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Filed number preserved for tax denominator. Real Splitflask product sales = $52,200. SGM 2025 1120-S reports ordinary loss -$32,900. Amazon 2025 is on SGM TIN (S054, $240,009.89 1099-K) but the 1099-K may not all be in this filed gross receipts (Amazon separately filed).</t>
+          <t>Filed number preserved for tax denominator. Real Splitflask product sales = $52,200. SGM 2025 1120-S reports ordinary loss -$32,900. Amazon 2025 is on SGM TIN (S054, $240,009.89 1099-K) but the 1099-K may not all be in this filed gross receipts (Amazon separately filed). | Layer 1 recon 2026-07-09: BANK-FEED IDENTITY CONFIRMED. Filed $130,976.23 = sum of 12 monthly deposit totals (per v11 SGM_2025_Sales_Reconstruction). Balance chain unbroken (S122-S133; each close = next open). Net change $492.38-$7,391.80=-$6,899.42 is consistent with deposits $130,976 and implied withdrawals $137,876. Artifact check CLEAN: no monthly deposit total is close to any 2025 SGM balance (max balance $7,391.80 &lt;&lt; any deposit-total). No negative implied-withdrawal months. Upgraded from provisional to provisional-footed. Cannot reach locked without per-statement transaction extraction (SGM_2025_Txns tab not built).</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Filed number overstates true sales. Corrected SPLT 2025 true sales = $279,815 (v11 Key_Findings 7/6/26). For tax amendment: needs full deposit classification (done per v11) and CPA decision. Kickstarter $54,386 is deferred revenue (fulfillment obligation), not earned revenue.</t>
+          <t>Filed number overstates true sales. Corrected SPLT 2025 true sales = $279,815 (v11 Key_Findings 7/6/26). For tax amendment: needs full deposit classification (done per v11) and CPA decision. Kickstarter $54,386 is deferred revenue (fulfillment obligation), not earned revenue. | Layer 1 recon 2026-07-09: The filed $369,980.87 is itself the FOOTED base (three-way match — see splt.2025.true_sales_net). Artifact check CLEAN. This figure is clean; the issue is not its accuracy but its composition (it includes non-revenue deposits). Status provisional (not locked) because the entity returns have not been finalized/amended. No change from prior status.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Source-built from full 11-statement SPLT 2025 bank classification. This is net-of-fees basis (what landed in bank minus platform fees already taken by Amazon/TikTok). Corrected per v11 Key_Findings 7/6/26.</t>
+          <t>Source-built from full 11-statement SPLT 2025 bank classification. This is net-of-fees basis (what landed in bank minus platform fees already taken by Amazon/TikTok). Corrected per v11 Key_Findings 7/6/26. | Layer 1 recon 2026-07-09: THREE-WAY MATCH CONFIRMED. SPLT 2025: revenue $369,980.87 - expenses $360,130.48 = net income $9,850.39 = Dec 31 2025 ending bank balance ($9,850.39). This constitutes an implicit annual-period footing proof that can only hold if deposits and withdrawals were correctly extracted. Artifact check CLEAN: max SPLT 2025 balance $15,450.93 is tiny relative to $369,981 total — any artifact would be a &lt;4% anomaly and would break the three-way match. The corrected $279,815 = $369,981 - $90,166 non-revenue is a classification derivation from the proved total. Status confirmed locked (no change). Balance chain S177-S188 unbroken.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -12385,7 +12385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13454,6 +13454,190 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>All 12 SGM 2024 months now foot to penny. Deduction totals recomputed from verified transaction set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sgm.2025.gross_receipts</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>status=provisional</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>status=provisional-footed</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Layer 1 bank-figure recon: sgm.2025.gross_receipts upgraded provisional→provisional-footed. Bank-feed identity confirmed (12 monthly deposits sum to filed $130,976.23; balance chain unbroken S122-S133; no artifact contamination).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sgm.2025.real_sales_net</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>status=provisional</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>status=provisional</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Layer 1 bank-figure recon: sgm.2025.real_sales_net no change (provisional). Artifact check clean. Classification-based figure; underlying total now provisional-footed. V12-eligible pending CPA confirmation of $78,776 exclusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>sgm.2025.gmv.wholesale</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>status=provisional-estimate</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>status=provisional-estimate</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Layer 1 bank-figure recon: sgm.2025.gmv.wholesale no change (provisional-estimate). Formula-based; no artifact risk; not V12-eligible without channel payout source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>splt.2025.gmv.intl_wires</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>status=provisional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>status=provisional</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Layer 1 bank-figure recon: splt.2025.gmv.intl_wires no change (provisional). Artifact check clean; wire amounts plausible vs monthly SPLT flows and &lt;&lt; account balances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>splt.2025.true_sales_net</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>status=locked</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>status=locked</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Layer 1 bank-figure recon: splt.2025.true_sales_net confirmed locked. Three-way match ($369,981 rev - $360,130 exp = $9,850 net = ending balance) holds. Artifact check clean. $279,815 derivation is clean classification from proved total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>splt.2025.gross_receipts_filed</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>status=provisional</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>status=provisional</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Layer 1 bank-figure recon: splt.2025.gross_receipts_filed unchanged (provisional). Filed total itself is clean (three-way match). No artifact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Layer1.BankFigureRecon</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SGM 2025: provisional-footed for $130,976 gross receipts; SPLT 2025: locked three-way match confirmed; intl wires and $52,200 artifact-clean</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Layer 1 2025 bank-derived figure reconciliation: footed balance chain, artifact checks run on all 6 bank-derived 2025 figures. No artifacts found. sgm.2025.gross_receipts upgraded to provisional-footed. splt.2025.true_sales_net locked status confirmed. All figures V12-eligible status documented.</t>
         </is>
       </c>
     </row>

--- a/Downloads/Splitflask-Financials/ledger.xlsx
+++ b/Downloads/Splitflask-Financials/ledger.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4026,6 +4026,581 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.emotive_io</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — Emotive.io SMS/Email Marketing charges</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3090.94</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>S327,S328,S329,S330,S332,S333,S334</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Jan $59.48, Feb $65.39, Mar $521.23+$341.62+$255.14+$257.93, Apr $348.81+$161.38, Jun $1,079.96 — all AmEx statements footed</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Shopify SMS/email marketing app. ⚠️ ENTITY ROUTING TJ: Shopify store on Personal TIN in 2024 → may be Personal Schedule C, not SGM. 6 bills in 9 months; spike Mar-Apr likely volume charges.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.marketing_allin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — ALL IN Podcast LLC sponsorship</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>500</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>S334</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Jul 22 2024 $500.00 ALL IN PODCAST LLC SAN FRANCISCO CA — AmEx CSV activity</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Podcast advertising/sponsorship. ⚠️ ENTITY ROUTING TJ: confirm entity (SGM vs Personal), confirm business purpose (Splitflask promotion vs personal).</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.hosting</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — Web Hosting (IONOS + GoDaddy)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>S327,S331,S333,S334</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>IONOS: Jan $17+$17 (verify if dup), May $17, Oct $17 = $68. GoDaddy: Aug $17.99. Total $85.99</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>⚠️ Jan has two IONOS $17 charges same day (01/11/24) — verify if duplicate or two separate domains/services. If dup, reduce by $17 to $68.99.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.shopify_sub</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — Shopify platform subscription</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>S327</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Jan 18 2024 SHOPIFY* 213269934 $64.16 — monthly platform fee</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>⚠️ ENTITY ROUTING TJ: Shopify store on Personal TIN in 2024 → Personal Schedule C deduction, not SGM.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.patent</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — PatentYogi patent services</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>152</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>S330</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Apr 17 2024 PAYPAL *PATENTYOGI 7814601177 $152.00 — patent research/filing services</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Likely SGM or shared patent work. Confirm entity and purpose with Riz/TJ.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.biz_clear</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — Clear business charges subtotal (no travel)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3893.09</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>S327,S328,S329,S330,S331,S332,S333,S334</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Emotive.io $3,090.94 + ALL IN $500 + IONOS+GoDaddy $85.99 + Shopify sub $64.16 + PatentYogi $152 = $3,893.09</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Travel ($570.57 Lyft/Uber/airlines) excluded pending entity/purpose confirmation. ⚠️ ENTITY SPLIT TJ: Emotive.io + Shopify sub likely Personal Sch C; PatentYogi + ALL IN + IONOS possibly SGM.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>amex.2024.netting.bank_payments_reclass</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — SGM bank CC_PAYMENT_AMEX → RECLASSED non-deductible</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-23676.3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>bank_reconciled</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>S327,S328,S329,S330,S331,S332,S333,S334</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>18 SGM bank entries (CC_PAYMENT_AMEX, $23,676.30) reclassed from expense to owner-draw/transfer. Deduction lives in AmEx charges above.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NETTING RULE: SGM bank paid AmEx bills ($23,676.30). The deductible amount = the underlying AmEx charges (only $3,893 business), NOT the full payment. The gap ($19,783) = SGM paying Riz's personal expenses → owner distribution. NEGATIVE value = reduces prior deduction base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>amex.2024.exp.net_amex_adjustment</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — Net adjustment to SGM deduction base</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-19783.21</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SGM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>S327,S328,S329,S330,S331,S332,S333,S334</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-$23,676.30 reclass of bank pmts + $3,893.09 biz charges = -$19,783.21 net. Use for neutrality recompute.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>⚠️ WARNING: Entity split further reduces SGM-specific increment. If Emotive.io ($3,091) + Shopify sub ($64) → Personal Sch C, SGM increment is only ~$720 (PatentYogi $152 + ALL IN $500 + hosting $68). SGM net = -$23,676 + $720 = -$22,956. NEGATIVE — worsens SGM neutrality gap. FULL PICTURE: (a) SGM deduction base DECREASES; (b) Personal Sch C GAINS ~$3,155 new deductions.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Splitflask</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>amex.2024.interest.nondeductible</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AmEx 2024 — Interest charges (NON-DEDUCTIBLE)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>9925.280000000001</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>S327,S328,S329,S330,S331,S332,S333,S334</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Monthly interest: Jan $905.13, Feb $922.78, Mar $979.26, Apr $960.67, May $989.08, Jun $957.19, Jul $980.87, Aug $1,062.01, Sep $976.03, Oct $407.35, Nov $389.63, Dec $395.28 = $9,925.28</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Interest on pre-existing Pay Over Time balance (~$49-52K since 2021). NOT deductible — personal credit card interest on personal debt. Underlying debt predates Splitflask.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4037,7 +4612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12374,6 +12949,302 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>S327</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>AMEX-2024-01-19.pdf</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AMEX-2024-01-19.pdf</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>AmEx Platinum Arize Nwosu acct -12004/-12012. Jan 2024 stmt closes 01/19/24. Prev bal $52,807.70, New charges $309.95, Pmts/credits -$4,427.20, Interest +$905.13, New bal $49,595.58. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>S328</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>AMEX-2024-02-18.pdf</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>AMEX-2024-02-18.pdf</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Feb 2024 stmt closes 02/18/24. Prev $49,595.58, Charges $117.08, Pmts -$1,699.02, Interest +$922.78, New bal $48,936.42. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>S329</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>AMEX-2024-03-20.pdf</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>AMEX-2024-03-20.pdf</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Mar 2024 stmt closes 03/20/24. Prev $48,936.42, Charges $1,599.56, Pmts -$2,229.82, Fees $40, Interest +$979.26, New bal $49,325.42. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>S330</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>AMEX-2024-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>AMEX-2024-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Apr 2024 stmt closes 04/19/24. Prev $49,325.42, Charges $814.83, Pmts -$2,392.43, Interest +$960.67, New bal $48,708.49. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>S331</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>AMEX-2024-05-20.pdf</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>AMEX-2024-05-20.pdf</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>May 2024 stmt closes 05/20/24. Prev $48,708.49, Charges $1,155.96, Pmts -$2,241.64, Interest +$989.08, New bal $48,611.89. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>S332</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>AMEX-2024-06-19.pdf</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>AMEX-2024-06-19.pdf</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Jun 2024 stmt closes 06/19/24. Prev $48,611.89, Charges $1,114.10, Pmts -$2,543.81, Fees $695, Interest +$957.19, New bal $48,834.37. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>S333</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>AMEX-2024-07-19.pdf</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>credit_card_stmt</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>AMEX-2024-07-19.pdf</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Jul 2024 stmt closes 07/19/24. Prev $48,834.37, Charges $1,223.37, Pmts -$2,583.61, Fees $29, Interest +$980.87, New bal $48,484.00. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>S334</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>AMEX-2024-activity (1-5 + base).csv</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>credit_card_activity</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>AMEX-2024-activity*.csv</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>6 AmEx activity CSVs covering Jun-Dec 2024 partial activity. Aug-Dec not covered by PDF stmts. Cards -12004 (Arize) + -12012 (Cheryl Benefield). 55 total rows.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12385,7 +13256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13641,6 +14512,131 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>amex.2024.reconstruction.footing</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ALL 7 AmEx 2024 PDF statements foot to the penny. Jan-Jul 2024. Zero parser bugs found — AmEx PDFs have single amount column (no balance-as-amount risk). Footing: prev_bal + charges + fees + interest - pmts = new_bal confirmed each month.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Step 1 AmEx 2024: statement footing complete. Sources S327-S333 marked reconciled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>amex.2024.reconstruction.classification</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AmEx 2024 classified: Business $3,893.09 (Emotive.io $3,090.94, ALL IN $500, IONOS+GoDaddy $85.99, Shopify sub $64.16, PatentYogi $152). Travel $570.57 (pending). Personal $2,898.25. Fees $735 (annual $695 + late fees net $0). Interest $9,925.28 non-deductible.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Step 2 AmEx 2024: charge classification. See Figures amex.2024.charges.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>sgm.2024.exp.cc_payment_amex.reclass</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CC_PAYMENT_AMEX $23,676.30 included in SGM 2024 deduction base</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CC_PAYMENT_AMEX $23,676.30 RECLASSED to non-deductible owner-draw/transfer. Deduction lives in AmEx underlying charges ($3,893.09 business). Gap $19,783 = SGM paying personal expenses = owner distribution.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Step 3 AmEx 2024 NETTING: per CLAUDE.md rule — deduct underlying charges, not bank payment. Reclass prevents double-count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sgm.2024.deduction_base.amex_net_impact</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Prior SGM 2024 corrected deduction base $614,321</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PRELIMINARY revised base $594,538 (= $614,321 - $23,676 + $3,893). FURTHER REDUCED if Emotive.io/Shopify routed to Personal Sch C: SGM base ~$591,365. AmEx is NOT the neutrality release valve — it worsens the gap.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Step 5 AmEx 2024: net deduction impact. Neutrality recompute deferred (TikTok fee still unsubstantiated). This figure is PRELIMINARY pending TJ entity routing call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>amex.2024.adspend.resolution</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ad spend additive-vs-overlapping open item</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AmEx 2024 carries ZERO ad spend (owner confirmed). AmEx Emotive.io = marketing SOFTWARE not media spend. De-duplicated 2024 ad spend: SGM bank $6,368 (Meta direct) + SGM card ···1400 $5,144.76 (pending confirmation it's incremental vs already in bank $6,368) + Cyberbrands card ···5130 $7,873.38 (separate entity). AmEx = $0 incremental ad.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Step 4 AmEx 2024: ad spend de-duplication. No AmEx overlap with any ad source.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13652,7 +14648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -14452,6 +15448,216 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>4 monthly ACH payments of $10,000 each from Shaed Inc (Mar-Jun 2024). Memo references "PO" and "Invoice SGM0051". Is Shaed Inc a wholesale customer (product sales) or consulting client (service income)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OI-AMEX-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AmEx 2024 entity routing: Emotive.io ($3,091) + Shopify sub ($64) → SGM or Personal Sch C?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Shopify store on Personal TIN in 2024. If Personal, SGM gains $0 from these; Personal Sch C gains $3,155. Affects which return claims the deduction.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.emotive_io; amex.2024.charges.shopify_sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OI-AMEX-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AmEx 2024 Jan IONOS double charge: two $17.00 charges on 01/11/24 — dup or two domains?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IONOS web hosting shows $17.00 twice on same day. If dup, reduce hosting total by $17 to $68.99.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.hosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OI-AMEX-03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ALL IN Podcast LLC $500 (Jul 22) — confirm Splitflask business purpose and entity</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Large single charge to podcast company. Is this a Splitflask ad/sponsorship (deductible) or personal media purchase? Confirm entity (SGM vs Personal).</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>amex.2024.charges.marketing_allin</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OI-AMEX-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AmEx Aug-Dec 2024 PDF statements missing — only CSV activity available</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PDF statements not provided for Aug-Dec. CSV data is partial. No formal footing possible for those months. Low risk as Aug-Dec charges are minimal and mostly personal.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Riz</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>S334</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OI-AMEX-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SGM neutrality gap WORSENED by AmEx reclass: base drops ~$22K-$20K not recovers</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AmEx was expected to be the release valve. Instead: CC_PAYMENT_AMEX $23,676 reclassed out (non-deductible), only $3,893 comes back in. Net -$19,783. If Emotive.io routes to Personal, SGM net = -$22,956. Neutrality gap now wider. TikTok fee ($68K potential) remains the only real lever.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>amex.2024.exp.net_amex_adjustment; Path B Step 4</t>
         </is>
       </c>
     </row>
@@ -14789,7 +15995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19992,6 +21198,444 @@
       <c r="M97" t="inlineStr">
         <is>
           <t>NEW coverage beyond S210. Opening $22,055.63 = S210 closing ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Jan 2024</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AMEX-2024-01-19.pdf</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S327</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>52807.70</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>49595.58</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Arize Nwosu personal card. SGM made payments from WF 8625. FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Feb 2024</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>AMEX-2024-02-18.pdf</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S328</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>49595.58</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>48936.42</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AMEX-2024-03-20.pdf</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S329</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>48936.42</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>49325.42</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Apr 2024</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AMEX-2024-04-19.pdf</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S330</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>49325.42</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>48708.49</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D102" t="n">
+        <v>5</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>May 2024</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AMEX-2024-05-20.pdf</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S331</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>48708.49</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>48611.89</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D103" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Jun 2024</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AMEX-2024-06-19.pdf</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S332</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>48611.89</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>48834.37</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D104" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Jul 2024</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AMEX-2024-07-19.pdf</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S333</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>48834.37</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>48484.00</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>FOOTED ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AmEx-12004</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Personal/SGM</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aug-Dec 2024</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AMEX-2024-activity*.csv</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>S334</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>AmEx Platinum (credit card)</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>CSV activity only — no PDF stmts for Aug-Dec; partial coverage (55 total CSV rows all 6 files)</t>
         </is>
       </c>
     </row>
